--- a/ALL/p11-out/Recipes.xlsx
+++ b/ALL/p11-out/Recipes.xlsx
@@ -1046,19 +1046,67 @@
           <t>fettuccine pasta, chicken breasts, olive oil, garlic, heavy cream, Parmesan cheese, salt, pepper, parsley, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0430085/7444c5f33e4.png</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430085/26efeaa0e0e.png</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430085/41052f8e97a.png</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430085/4a14af66e8b.png</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0430085/12f81634e67.png</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
       <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr"/>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0430085/01386094016.png</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430085/57eaf00c8e1.png</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430085/a52beba7d15.png</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430085/542504fe280.png</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0430085/dd8c11c981d.png</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
       <c r="T4" t="inlineStr"/>
     </row>
   </sheetData>

--- a/ALL/p11-out/Recipes.xlsx
+++ b/ALL/p11-out/Recipes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="27">
   <si>
     <t>Title</t>
   </si>
@@ -23,6 +23,21 @@
   </si>
   <si>
     <t>Generated At</t>
+  </si>
+  <si>
+    <t>Statut Article</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>article_title</t>
+  </si>
+  <si>
+    <t>id_article</t>
+  </si>
+  <si>
+    <t>Json Recipe</t>
   </si>
   <si>
     <t>Spicy Honey Glazed Salmon</t>
@@ -130,6 +145,552 @@
   </si>
   <si>
     <t>2026-04-30 07:25:29</t>
+  </si>
+  <si>
+    <t>DONE ARTICLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Spicy Honey Glazed Salmon Recipe: A Quick and Easy Delight
+## Introduction
+The allure of a perfectly cooked salmon fillet is undeniable, especially when it is generously glazed with a spicy and sweet honey sauce. This Spicy Honey Glazed Salmon recipe is not only quick and easy to prepare but also packs a punch of flavor that will elevate your dinner table. Whether you're looking for something special to impress guests or simply aiming for an enjoyable weeknight dinner, this dish delivers on both flavor and convenience. Its Asian-inspired elements promise to delight the palate, combining various tastes that blend seamlessly, creating a truly memorable meal.
+The beauty of this dish lies in its simplicity. Within just 25 minutes, you can bring a restaurant-quality entrée to your dining table with minimal effort. The recipe is accessible to cooks of all skill levels, from beginners to seasoned chefs, making it an ideal choice for anyone looking to expand their culinary repertoire. The balance of sweet and spicy flavors in the glaze complements the rich taste of the salmon, offering a satisfying yet refreshing experience with each bite. 
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 15 minutes
+- Total Time: 25 minutes
+- Course: Main Course
+- Cuisine: Asian-Inspired
+- Servings: 4
+- Calories: ~350 per serving
+## Ingredients
+- 4 salmon fillets
+- 1/4 cup honey
+- 2 tablespoons soy sauce
+- 1 tablespoon sriracha
+- 1 tablespoon olive oil
+- 2 cloves garlic, minced
+- 1 teaspoon ginger, grated
+- Salt and pepper to taste
+- Chopped green onions for garnish
+{{image_ing_1}}
+## Instructions
+1. Preheat your oven to 400°F (200°C).
+2. In a small bowl, whisk together honey, soy sauce, sriracha, olive oil, garlic, and ginger until well combined.
+3. Season the salmon fillets with salt and pepper on both sides.
+4. Place the salmon fillets skin-side down on a lined baking sheet.
+5. Brush the spicy honey glaze generously over the salmon fillets.
+6. Bake in the preheated oven for 12-15 minutes, or until the salmon flakes easily with a fork.
+7. Remove from the oven and let it rest for a few minutes.
+8. Drizzle any remaining glaze over the top and garnish with chopped green onions.
+9. Serve with your choice of side dishes.
+The recipe's success hinges on straightforward preparation and high-quality components. With its short list of ingredients, it is easy to see why this Spicy Honey Glazed Salmon has become a favorite. In addition to being delicious, it also presents the opportunity to explore the complexities of Asian-inspired flavors, creating a meal that resonates not just with gourmet taste but also with a rich cultural palate.
+### Flavor Profile
+The flavor profile of this dish is one of its most exciting features. The combination of honey and sriracha creates a delightful balance of sweetness and heat, resulting in a glaze that tantalizes the taste buds. The honey lends a rich, floral sweetness that perfectly counteracts the spicy kick delivered by sriracha. Together, they create a sauce that is both bold and inviting, coaxing even the pickiest eaters to indulge. 
+In addition to the glaze, the fresh garlic and ginger add aromatic notes that elevate the dish further. Garlic offers its distinctive pungency, while ginger contributes a zesty warmth that brightens the overall flavor. This combination makes for a dish that feels indulgent yet is incredibly straightforward to prepare.
+### Cooking Method
+The cooking method for the Spicy Honey Glazed Salmon is baking, which is a popular technique that ensures even cooking while allowing the flavors of the glaze to infuse the fish. Baking at 400°F creates a hot environment that seals in moisture, preventing the salmon from drying out. This method not only enhances the flavor but also eases the cooking process, as you can focus on other preparations while the oven does its job.
+Moreover, the high temperature of baking leads to a delightful caramelization of the honey glaze, giving the top of the salmon a beautifully shiny finish. As it bakes, the fish becomes tender and flaky, allowing it to absorb the sweetness and spice of the glaze for a truly rewarding culinary experience.
+### Nutritional Benefits
+When it comes to nutrition, salmon stands out as a fantastic protein source. It is rich in omega-3 fatty acids, essential for heart health, making it a cornerstone of a balanced diet. Additionally, this fish is packed with high-quality protein and essential nutrients, including vitamins B12 and D, which contribute to overall well-being. 
+The ingredients in the glaze also provide nutritional perks. For instance, honey contains antioxidants and has been linked to various health benefits, including anti-inflammatory properties. Meanwhile, the ginger and garlic add not only flavor but also health benefits, as they are known for their anti-inflammatory and immune-boosting qualities. This combination makes the Spicy Honey Glazed Salmon a delicious meal that also supports a healthy lifestyle.
+## Ingredients
+In the following sections, we'll delve deeper into the main ingredients used in your Spicy Honey Glazed Salmon, discussing their importance and what to look for when sourcing them for your dish. 
+### Main Ingredients
+The cornerstone of this recipe, the salmon fillets, should be fresh to guarantee the best flavor and texture. When purchasing salmon, look for fillets that are firm to the touch, with bright, moist skin. Avoid any pieces that appear dull or dry; the color should be vibrant. 
+Honey is another main ingredient in this recipe. There are various types of honey available, each bringing different flavor notes to the dish. While clover honey is a common choice, experimenting with unique varieties like wildflower or eucalyptus can add a distinct twist to your glaze.
+Soy sauce is essential for providing a savory umami flavor that contrasts beautifully with the sweetness of honey. Low-sodium varieties are available for those looking to control salt intake without sacrificing taste.
+### Sauce Components
+The spiciness of the dish comes primarily from sriracha, a type of hot sauce made from chili peppers, vinegar, garlic, and sugar. Depending on your tolerance for heat, you can adjust the amount of sriracha you use, making the dish as fiery or mild as you like. 
+Both garlic and ginger contribute significantly to the flavor and aromatic quality of the glaze. While fresh ingredients are encouraged for the best flavor, if you’re short on time, pre-minced garlic and powdered ginger can serve as substitutes, though they may slightly alter the final taste.
+### Seasoning and Garnish
+A simple seasoning of salt and pepper is all it takes to enhance the natural flavors of the salmon. It’s important to season the fillets on both sides for an even taste. Lastly, chopped green onions serve as a fresh and crunchy garnish, adding a pop of color and flavor. They can be sprinkled on just before serving for a crisp finish that complements the glazed salmon wonderfully. 
+In the following section, we will explore the preparation steps necessary for crafting the perfect Spicy Honey Glazed Salmon, complete with tips and tricks to help you achieve the best results.
+### Best practices for serving
+Serving Spicy Honey Glazed Salmon is an opportunity to impress your guests with both its stunning presentation and delectable flavor. When plated correctly, the colors and textures of the dish can enhance its appeal. Start by placing each salmon fillet on a warm plate; this helps maintain the dish's temperature and provides a more enjoyable dining experience. 
+Drizzle any remaining sweet and spicy glaze over the top of the salmon fillets to add shine and an extra layer of flavor. Garnishing with freshly chopped green onions not only introduces a pop of color but also adds a mild onion flavor that elevates the overall taste profile. Consider serving the salmon with a wedge of lemon on the side, allowing diners to squeeze fresh juice over their fish, adding a bright acidity that complements the honey glaze beautifully.
+## Flavor Enhancements
+Exploring various ways to customize and enhance flavors in the Spicy Honey Glazed Salmon can appeal to diverse palates and take this dish to the next level. The great thing about the base recipe is its versatility.
+### Heat Level Adjustments
+To cater to different taste preferences, you can easily adjust the heat level of the dish. While sriracha provides a good kick, consider experimenting with different hot sauces to discover new flavor combinations. For instance, using a smoky chipotle hot sauce can bring an exciting dimension to the glaze. 
+Additionally, if you prefer a little extra heat, sprinkle some chili flakes over the salmon before baking. This simple addition can build complexity and deeper heat without overpowering the sweetness of the glaze.
+### Sweetness Variations
+While honey is a key ingredient, switching to different types of honey can yield delightful variations in flavor. For instance, using wildflower honey gives a more floral note, whereas buckwheat honey imparts a richer, earthier taste. 
+Alternatively, consider mixing in other sweet elements, such as maple syrup, to introduce a warm, caramelized flavor alongside the honey. This combination will offer a delightful balance and complexity that can enhance your original recipe.
+### Herb and Spice Additions
+Adding fresh herbs and additional spices can elevate the dish significantly. Incorporating freshly chopped cilantro or parsley as a garnish can provide a burst of freshness. 
+You might also consider sprinkling toasted sesame seeds over the glazed salmon just before serving. This adds both a textural crunch and a nutty flavor that pairs superbly with the dish's existing elements.
+## Suggested Side Dishes
+Complementary side dishes can enhance your meal and create a well-rounded dining experience. Several options pair excellently with Spicy Honey Glazed Salmon.
+### Rice Pairings
+Rice is a classic accompaniment to salmon, and choosing the right type can make a notable difference. Jasmine rice, with its floral aroma and slightly sticky texture, is an ideal match, providing a perfect canvas for the spicy glaze. 
+Alternatively, basmati rice, known for its nutty flavor, can offer a delightful contrast. Cooking methods significantly impact the end result; aim to rinse the rice before cooking to remove excess starch for light and fluffy grains. You may try cooking the rice in a broth or adding a bay leaf for extra depth of flavor.
+### Vegetable Options
+Adding vegetables not only balances the meal but also boosts its nutritional value. Offering sautéed or steamed vegetables, like broccoli or snap peas, provides a bright and crunchy contrast to the tender salmon. 
+For added texture and flavor, consider roasting vegetables such as Brussels sprouts or sweet potatoes. The caramelization achieved during the roasting process harmonizes wonderfully with the sweet and spicy notes of the glazed salmon.
+### Salad Pairings
+To refresh the palate, a fresh salad is an excellent companion. A simple arugula salad dressed with olive oil, lemon juice, and a sprinkle of salt can create a light and zesty counterbalance to the sweetness of the salmon.
+Another option is a cucumber salad, where thinly sliced cucumbers tossed in rice vinegar and sesame oil can offer a cooling element that pairs nicely with the dish. 
+## Storage and Reheating
+Storing leftover Spicy Honey Glazed Salmon correctly ensures you can enjoy the dish at a later time without sacrificing flavor or texture.
+### Refrigeration Tips
+To refrigerate leftover salmon, place it in an airtight container to prevent it from drying out and absorbing other odors in the fridge. Properly stored, the salmon can last for up to 2 days, maintaining its quality and flavor. 
+### Reheating Methods
+When it comes to reheating, it's essential to avoid drying out the salmon. The stovetop can be an excellent option, as it allows for controlled heat application. Gently heat the fillets in a non-stick skillet over low heat. Alternatively, using an oven can help maintain moisture; preheat it to around 300°F (150°C) and reheat the salmon until warmed through.
+### Freezing Guidelines
+If you're looking to store the salmon for a more extended period, freezing is an option. Wrap each salmon fillet tightly in plastic wrap, then place them in a freezer-safe container. It’s advisable to consume frozen salmon within 2-3 months for optimal taste. 
+To thaw, move the salmon from the freezer to the refrigerator and let it sit overnight, or for a quicker option, use the microwave's defrost setting. After thawing, follow the reheating methods mentioned above for the best results.
+## Potential Variations
+If you're interested in branching out, there are several creative variations of Spicy Honey Glazed Salmon to explore.
+### Alternative Proteins
+Using alternative proteins like chicken or tofu can create different experiences with the same delightful glaze. If opting for chicken, choose breasts or thighs and adjust cooking times accordingly to ensure they reach a safe internal temperature. For tofu, press out the moisture and cut into cubes or slabs, then pan-sear or bake until golden.
+### Different Cooking Methods
+While the oven method offers simplicity, exploring other cooking methods can provide excellent results. Grilling salmon can impart irresistible smoky flavors while adding grill marks for a visually appealing dish. 
+Pan-searing can also be considered; this method allows for a crispy skin on the salmon fillets, enhancing the overall enjoyment of the dish. 
+### Marinade Options
+To extend the flavor of the glaze even further, consider using it as a marinade. Marinating the salmon (or chicken) for 30 minutes can deepen the flavors substantially. Ensure you use the same ingredients in your marinade to maintain the original taste profile, but feel free to add a touch of citrus for an extra zesty kick.
+## Final Thoughts on Spicy Honey Glazed Salmon
+Spicy Honey Glazed Salmon is a wonderfully balanced dish that brings together savory, sweet, and spicy elements harmoniously. The ease of preparation, with the total time required being just 25 minutes, makes it an excellent option for both weeknight dinners and entertaining guests. The delightful combination of flavors, along with the tender salmon, ensures a satisfying meal that is quick to prepare and sure to impress.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Spicy Pesto Pizza: A Flavorful Italian Classic
+## Introduction
+Spicy Pesto Pizza is a delightful dish that marries the beloved Italian classic of pizza with the vibrant kick of spicy pesto. This combination creates a unique flavor profile that is sure to satisfy not only pizza lovers but also those who enjoy a bit of spice in their meals. The rich and zesty notes of the spicy pesto sauce serve as a wonderful base, complemented perfectly by the melted mozzarella cheese and the fresh, juicy bite of cherry tomatoes. 
+This pizza is not just about savory flavors; it’s also visually appealing, making it a perfect centerpiece for any gathering. Whether you’re hosting a casual family dinner, a game night, or a festive celebration, this spicy twist on a traditional pizza will certainly impress your guests. Originating from the heart of Italian cuisine, the adoption of spicy pesto in this dish offers a modern twist that enhances its traditional roots, giving it a contemporary edge that attracts both classicists and adventurous eaters alike.
+## Recipe Overview
+- Prep Time: 15 minutes
+- Cook Time: 15 minutes
+- Total Time: 30 minutes
+- Course: Main Course
+- Cuisine: Italian
+- Servings: 4
+- Calories: ~350 per serving
+The key characteristics of Spicy Pesto Pizza lie in its simple yet high-quality ingredients. The pizza dough can be either store-bought or homemade, making it accessible for every cook. The spicy pesto sauce, which is the star of this dish, not only lends a fiery flavor but also brings a vibrant green color that contrasts beautifully with the white of the mozzarella cheese and the colorful toppings.
+The cooking process is straightforward and quick, allowing for a satisfying pizza experience in just about half an hour. With a baking time of only 12-15 minutes, you can expect a crispy crust, bubbling cheese, and breaching aromas, setting the stage for an enticing meal. This pizza offers versatility—not only can it be a standout main dish for a laid-back evening at home, but it can also shine as a highlight during gatherings and celebrations where food is the focal point.
+## Ingredients
+- 1 pizza dough (store-bought or homemade)
+- 1/2 cup spicy pesto sauce
+- 1 cup shredded mozzarella cheese
+- 1/2 cup sliced cherry tomatoes
+- 1/4 cup sliced black olives
+- 1/4 teaspoon red pepper flakes
+- Fresh basil leaves for garnish
+To create this hearty pizza, the ingredients are simple yet impactful, with the spicy pesto sauce being the standout component that enhances the overall flavor. The shredded mozzarella provides a creamy texture that beautifully balances the heat from the spicy pesto and the red pepper flakes. Complementing these flavors are the fresh cherry tomatoes, which add sweetness, and black olives, offering an additional layer of richness. Finally, garnishing with fresh basil not only adds a pleasant aromatic quality but also elevates the pizza’s presentation.
+{{image_ing_1}}
+## Instructions
+1. Preheat your oven to 475°F (245°C).
+2. Roll out the pizza dough on a floured surface to your desired thickness.
+3. Transfer the rolled dough to a pizza stone or baking sheet lined with parchment paper.
+4. Spread the spicy pesto sauce evenly over the pizza dough.
+5. Sprinkle the shredded mozzarella cheese on top of the pesto.
+6. Arrange the sliced cherry tomatoes and black olives over the cheese.
+7. Sprinkle the red pepper flakes for an extra kick.
+8. Bake in the preheated oven for 12-15 minutes or until the crust is golden and the cheese is bubbly.
+9. Remove from the oven and let it cool for a couple of minutes.
+10. Garnish with fresh basil leaves before slicing.
+11. Serve hot and enjoy your spicy pesto pizza!
+Preparation is key in achieving a great pizza, so let’s delve into the initial steps to ensure your Spicy Pesto Pizza turns out perfectly.
+### Importance of preparation before cooking
+Having all your ingredients ready before you start cooking can significantly impact the outcome of your dish. When it comes to pizza, the assembly should be efficient yet thoughtful, ensuring even distribution of textures and flavors. 
+### Preheating the Oven
+Setting your oven to 475°F (245°C) is crucial for achieving the perfect crispy crust. The high temperature allows the pizza to bake quickly, helping the cheese to melt without drying out the dough.
+### Rolling Out the Pizza Dough
+When rolling out the pizza dough, consider the desired thickness—thicker crusts may require longer baking time while thinner crusts will cook more quickly. Use a floured surface to prevent sticking, and don’t be afraid to stretch the dough to reach the desired size, ensuring it’s even and consistent for uniform cooking.
+### Transferring Dough
+After you’ve rolled out the dough, it’s time to transfer it carefully to a pizza stone or a baking sheet lined with parchment paper. This step requires a gentle touch to prevent the dough from tearing. The choice between a pizza stone and a baking sheet can influence your pizza’s final texture, with the stone ideally distributing heat evenly for that perfect crust.
+As we progress through the recipe, spreading the spicy pesto sauce is next on the list, which truly sets the foundation for the flavor explosion that follows. 
+Stay tuned for Part 2, where we will dive deeper into the sauce application and the assembly of toppings that bring this pizza to life!
+### Techniques for an even spread
+Achieving an even spread of your spicy pesto sauce on the pizza dough is crucial for flavor distribution. Start by using the back of a spoon or an offset spatula to gently spread the sauce, ensuring that you cover every inch of the dough. This technique not only allows for better control but also helps in achieving a consistent layer, preventing any dry spots that could affect the overall taste of the pizza. Remember that a thin, even layer is preferable; applying too much pesto can lead to a soggy crust, which is not desirable. 
+### Suggestions for making homemade spicy pesto
+Creating a homemade spicy pesto can elevate your Spicy Pesto Pizza to a whole new level. If you decide to go this route, begin with fresh basil, garlic, and a handful of nuts such as pine nuts or walnuts. Combine these with olive oil for smoothness. To add heat, incorporate red chili flakes or even a fresh chili pepper blended into the mixture. You can adjust the spice according to your taste preference, giving you control over the final flavor profile. A pinch of Parmesan cheese can add richness, but it’s optional based on dietary restrictions.
+## Adding the Toppings
+### Arrangement of Ingredients
+When layering the ingredients on your pizza, the arrangement matters significantly. Begin with the spicy pesto as your base, followed by the mozzarella cheese, which serves as a barrier to keep the crust crispy. Over the cheese, add your cherry tomatoes and black olives strategically. This will create a stunning mosaic of colors and flavors, ensuring every slice offers a delicious variety.
+### Mozzarella Cheese Layering
+The mozzarella cheese layer is a key component of this pizza. Sprinkling the cheese evenly on top of the pesto helps promote even melting and browning during baking. A full cup of shredded mozzarella allows for a perfect combination of creamy texture while pulling apart nicely with each bite. This ensures that each slice is as indulgent as the last.
+### Ideal amount for meltiness and texture
+Using the right amount of cheese is essential for achieving that classic pizza meltiness. A cup is generally sufficient; too much cheese can lead to a greasy surface, while too little may leave the pizza feeling dry. The cheese should be distributed so there is enough coverage over the pesto and toppings, providing that cheesy goodness everyone loves.
+### Cherry Tomatoes and Black Olives
+Cherry tomatoes and black olives are not just colorful features—they play a vital role in enhancing the pizza’s overall flavor. The burst of sweetness from the cherry tomatoes complements the spiciness of the pesto beautifully, while the briny flavor of black olives adds depth. When sliced and spread across the pizza, their vibrant colors create an unmatched visual appeal, making your homemade pizza look just as good as it tastes.
+### Red Pepper Flakes
+For those who enjoy a little extra kick, incorporating additional red pepper flakes is an excellent option. The original recipe includes 1/4 teaspoon, but feel free to sprinkle more if desired. To personalize the heat level, consider offering a side of red pepper flakes at the table, allowing guests to adjust their servings to their own preferences. This customization can make your Spicy Pesto Pizza enjoyable for all taste preferences, from mild to wild.
+## Baking the Pizza
+### Optimal Baking Conditions
+Baking your Spicy Pesto Pizza at the appropriate temperature is one of the keys to achieving the best results. Preheating your oven to 475°F (245°C) creates a hot environment that is ideal for cooking the pizza thoroughly while providing that perfect crispy crust. If you’re using a pizza stone, let it heat in the oven for at least 30 minutes for optimal results.
+### Time range for baking for a perfect crust
+Bake your pizza for 12-15 minutes; this timing is ideal for ensuring that both the crust and toppings are cooked to perfection. Keep an eye on your pizza toward the end of this timeframe, as oven conditions may vary slightly. Adjusting for personal preference, some individuals may prefer a longer bake for an extra crispy crust.
+### Recognizing signs of readiness (golden crust and bubbly cheese)
+To determine if your pizza is ready to come out of the oven, look for a golden-brown crust and bubbling cheese. The edges should be firm yet slightly crispy, and the cheese should have melted beautifully with little to no separation from the toppings. This visual check is reliable and ensures every bite is enjoyable.
+## Cooling and Garnishing
+### Cooling Process
+Once you’ve successfully baked your pizza, give it a brief cooling period of about 2-3 minutes before slicing. This waiting period allows the cheese to set slightly, making it easier to cut into clean slices without the toppings sliding off. 
+### Importance of letting the pizza cool slightly after baking
+Letting your pizza cool slightly also enhances the eating experience. The initial contact with hot cheese and toppings can be overwhelming. Allowing the pizza to rest allows the flavors to settle and blend more harmoniously.
+### Garnishing with Basil
+Fresh basil leaves aren’t just for looks; they add an aromatic quality that can elevate the overall flavor profile of your pizza. After cutting the pizza, sprinkle fresh basil leaves on top. Their vibrant color and fragrant scent contribute to the pizza’s appeal, making it an inviting dish.
+### Enhancing aroma and presentation
+Incorporating basil at the end of the cooking process maximizes its flavor while ensuring the leaves retain their bright green color. This finishing touch transforms your Spicy Pesto Pizza into a visually stunning centerpiece that is pleasing to the eye and the palate.
+## Serving Suggestions
+### Ideal pairings for Spicy Pesto Pizza
+When serving Spicy Pesto Pizza, consider pairing it with a light arugula salad dressed with lemon vinaigrette. The peppery notes of arugula complement the creamy cheese and spicy pesto, providing a refreshing balance. 
+### Side dishes or beverages that complement the dish
+For beverages, a chilled white wine like Pinot Grigio or a light Italian beer can enhance the meal. If you're opting for non-alcoholic options, sparkling water with a slice of lemon can cleanse the palate and offer a delightful contrast.
+## Variations and Customizations
+### Exploring variations with different toppings
+Feel free to get creative when it comes to toppings. For a meat-lover's twist, consider adding cooked Italian sausage or pepperoni. Alternatively, for a vegetarian option, sautéed mushrooms or spinach can introduce different textures and flavors without overshadowing the existing ingredients.
+### Options for dietary preferences, such as vegan or gluten-free adaptations
+For those with dietary restrictions, the recipe can easily be adapted. Using a gluten-free pizza crust allows those with gluten sensitivity to enjoy this dish without worry. To make a vegan version, opt for cashew cheese or a plant-based mozzarella alternative, ensuring that the spicy pesto remains dairy-free.
+## Storage and Reheating Tips
+### Best practices for storing leftovers
+If you happen to have leftovers, store them in an airtight container in the refrigerator for up to 3 days. Ensuring the pizza is cooled before storage will help maintain its freshness and prevent sogginess.
+### Methods for reheating pizza while preserving texture and flavor
+To reheat the pizza while preserving its crust and melt-in-your-mouth cheese, use an oven or a skillet. Preheat the oven to 350°F and warm for about 10 minutes. Alternatively, use a skillet on medium heat to crisp up the crust while allowing the toppings to warm through adequately.
+## Conclusion
+Spicy Pesto Pizza is not just a meal; it's an experience filled with vibrant flavors and textures that cater to a wide array of preferences. With its quick preparation and cooking time, it stands out as a convenient yet indulgent dish that can make any mealtime special. The harmonious blend of spices, fresh ingredients, and melted cheese creates a pizza that is both comforting and exciting.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Creamy Garlic Chicken Pasta Recipe
+## Introduction
+Creamy Garlic Chicken Pasta is a delightful dish that combines tender chicken, rich cream, and wholesome fettuccine, making it a perfect main course for any occasion. This recipe brings together Italian flavors in a quick and easy way, ensuring a satisfying meal that doesn’t take hours to prepare. The vibrant appearance of the dish, paired with its delicious taste, is sure to please both family and guests alike.
+The luscious cream sauce enveloping the pasta is elevated by the aromatic essence of garlic, embodying the comforting yet elegant nature of classic Italian cuisine. It is a dish that effortlessly bridges the gap between everyday dinners and special occasions, creating a culinary experience that feels both indulgent and accessible.
+Whether you are aiming to impress at a dinner party or need a cozy weeknight meal, Creamy Garlic Chicken Pasta serves as a versatile option. Each bite features a medley of flavors and textures, making it a favorite among pasta lovers.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 20 minutes
+- Total Time: 30 minutes
+- Course: Main Course
+- Cuisine: Italian
+- Servings: 4
+- Calories: ~600 per serving
+Creamy Garlic Chicken Pasta is not just a dish; it's an experience that encapsulates the essence of Italian cuisine. In this section, we delve into what makes this pasta dish unique and the flavor profile that enhances its appeal.
+### Description of the Dish
+The creamy texture of the sauce is a hallmark of this dish, with a balance of savory flavors accentuated by the slight nuttiness of the Parmesan cheese and the pungent heat of minced garlic. The combination of these ingredients creates a rich and silky sauce that coats the fettuccine beautifully.
+### Cooking Method
+The skillet cooking technique used in this recipe provides both efficiency and flavor. The chicken is seared to perfection, locking in moisture and developing a slight crust that adds a delightful contrast to the creamy sauce that follows. Sautéing the garlic in the same skillet allows the flavors to meld, creating a harmonious base for the dish. The final simmer with the cream and cheese creates a thick and luxurious sauce that binds the ingredients together.
+### Serving Suggestions
+Creamy Garlic Chicken Pasta pairs excellently with a light salad, such as a simple arugula or mixed green salad, offering freshness to balance the rich flavors of the pasta. A loaf of crusty bread is also an ideal companion for mopping up the remaining sauce on your plate. For those who enjoy wine, consider pairing this dish with a crisp white wine, like a Pinot Grigio or a light Chardonnay, which can complement the creamy texture and enhance the overall dining experience.
+## Ingredients
+A successful dish starts with high-quality ingredients. This section provides a detailed list of what you'll need to create this creamy delight.
+- 8 oz fettuccine pasta
+- 2 boneless, skinless chicken breasts
+- 3 tablespoons olive oil
+- 4 cloves garlic, minced
+- 1 cup heavy cream
+- 1 cup grated Parmesan cheese
+- Salt and pepper to taste
+- Fresh parsley, chopped (for garnish)
+### Pasta
+The focal point of this dish is the fettuccine pasta. At 8 ounces, this quantity provides a robust base to absorb the creamy sauce. Fettuccine, with its flat and wide shape, is particularly adept at holding onto sauces, making it an excellent choice for this recipe.
+### Chicken
+Using 2 boneless, skinless chicken breasts ensures even cooking and a tender texture. This cut is favored in recipes like this due to its ability to stay juicy while still providing substantial flavor, enriching the overall profile of the dish with each bite.
+### Aromatics and Fats
+The dish begins with 3 tablespoons of olive oil, which not only serves as the cooking fat but also infuses the chicken and garlic with rich flavor. The 4 cloves of minced garlic are pivotal in adding that beloved aromatic quality that keeps this dish classic. 
+### Creamy Base
+The luxurious sauce is achieved with 1 cup of heavy cream, which creates the rich texture that defines this pasta dish. As the cream simmers, it melds with 1 cup of grated Parmesan cheese, enhancing the depth of flavor and providing a creamy consistency that perfectly coats the fettuccine.
+### Seasoning
+For seasoning, salt and pepper to taste are crucial. These simple ingredients should not be overlooked, as they elevate the dish by enhancing each component’s natural flavors. The fresh parsley offers a finishing touch as a garnish, lending freshness to the presentation and an additional layer of flavor.
+{{image_ing_1}}
+## Instructions
+1. Cook the fettuccine pasta according to package instructions until al dente. Drain and set aside.
+2. Season the chicken breasts with salt and pepper on both sides.
+3. In a large skillet, heat the olive oil over medium heat. Add the chicken breasts and cook for about 6-7 minutes on each side, or until fully cooked. Remove from skillet and let rest.
+4. In the same skillet, add the minced garlic and sauté for about 1 minute until fragrant.
+5. Pour in the heavy cream and bring to a gentle simmer. Stir in the Parmesan cheese until melted and smooth.
+6. Slice the cooked chicken into strips and add it to the creamy sauce. Stir to combine.
+7. Add the cooked fettuccine to the skillet and toss until the pasta is well coated in the sauce.
+8. Adjust seasoning with additional salt and pepper if needed.
+9. Serve hot, garnished with chopped fresh parsley.
+## Preparing the Pasta
+The preparation of the pasta is a crucial step that must be done correctly to create the perfect base for the dish. Cooking the fettuccine to an al dente texture, means it retains some firmness that complements the creaminess of the sauce. Timing and following package instructions closely is essential to achieving the ideal texture.
+## Cooking the Chicken
+Properly cooking the chicken is essential for both flavor and texture in the dish. Starting with good seasoning is key; salt and pepper will enhance its natural taste, allowing the flavors of the chicken to shine through. Following with a careful cooking technique ensures the chicken remains tender and juicy while developing a beautiful golden color. Maintaining medium heat during cooking helps to create an even, cooked-through breast without drying it out.
+## Importance of Resting the Chicken After Cooking
+Once the chicken breasts are cooked to perfection, allow them to rest for a few minutes before slicing. Resting is crucial because it helps the juices redistribute throughout the meat. This way, when you slice into the chicken, you retain moisture and ensure a more tender bite. If you slice too soon, the juices can spill out, leaving you with dry chicken, which is certainly not desirable in this creamy dish.
+Resting for about 5-10 minutes is ideal. Cover the chicken loosely with aluminum foil to keep it warm while it rests. This step may seem small, but it significantly impacts the overall taste and texture of your Creamy Garlic Chicken Pasta.
+## Making the Sauce
+Creating the sauce is where the creamy goodness comes to life, transforming simple ingredients into a dish that feels luxurious.
+### Sautéing Garlic
+When it comes to sautéing garlic, technique is essential to avoid burning while still enhancing the flavor. Start by heating your skillet to medium heat and adding the olive oil before introducing the minced garlic. Sauté it gently; remember that garlic cooks quickly and can become bitter if overcooked.
+Cook the garlic for about 1 minute, stirring frequently, until it becomes fragrant and slightly golden. A quick tip is to keep a close eye on the garlic as it cooks—this is where many cooks go wrong. Garlic can rapidly turn from perfectly fragrant to burnt, so don’t leave it unattended. 
+### Creating a Creamy Base
+Once the garlic has been sautéed, it's time to add the heavy cream. Pour it into the skillet and bring to a gentle simmer, which will help integrate the garlic flavor into the sauce. Be sure to stir continuously to prevent the cream from sticking to the bottom of the pan. 
+After simmering for a minute or two, stir in the grated Parmesan cheese. This step is vital in ensuring a smooth texture for your sauce. The cheese will melt into the cream, creating that luscious, silky base that gives the dish its characteristic creamy richness. If necessary, adjust the heat as you add the cheese to maintain a gentle simmer without boiling.
+## Combining the Ingredients
+The final assembly of the dish brings together all elements for the ultimate creamy experience, transforming individual components into a harmonious meal.
+### Slicing the Chicken
+When it’s time to slice the rested chicken, aim for even, bite-sized strips. Using a sharp knife, slice against the grain of the meat. This technique results in more tender pieces that are easier to chew and mix into the pasta. Proper slicing not only enhances the eating experience but also presents beautifully when arranged on the pasta.
+### Tossing Pasta in Sauce
+Now it’s time to combine everything. Once the chicken is sliced and the creamy sauce is ready, add the cooked fettuccine directly to the skillet. Gently toss the pasta in the sauce, making sure every strand is well-coated. The key here is to use a pair of tongs or two forks to toss the pasta delicately without breaking it.
+Adjusting the seasoning during this stage is crucial. Taste the pasta and sauce, and feel free to add more salt and pepper to perfect the flavor. This ensures that each bite is bursting with the intended savory and creamy goodness.
+## Presentation and Garnish
+The way the dish is presented can elevate the dining experience, making it visually appetizing and enhancing anticipation for the meal.
+### Plating the Pasta
+When plating your creamy garlic chicken pasta, aim for balanced portions. Start by placing a generous amount of pasta in the center of the plate. Use a fork to twirl some of the fettuccine to create height and volume on the plate, which is visually appealing.
+Consider using a large, flat plate or bowl to allow the creamy sauce to shine rather than being confined within a smaller dish. This technique not only looks professional but also allows the sauce to pool beautifully around the pasta.
+### Garnishing with Parsley
+Finally, garnish your pasta dish with freshly chopped parsley. Not only does it add a vibrant pop of color, but it also provides a fresh, herbal note that balances the richness of the pasta. Sprinkling parsley over the top of the dish can elevate its aesthetic appeal, making it look restaurant-worthy.
+Use a light hand with the garnish for the best effect. Too much can overwhelm the dish, while just the right amount enhances both visual appeal and flavor.
+## Taste Profile
+This section explores the flavor dynamics that make Creamy Garlic Chicken Pasta so irresistible.
+### Creaminess vs. Savory
+The base of the dish provides a delightful interplay between creaminess and savory notes. The heavy cream offers a luscious mouthfeel, while the Parmesan adds depth and richness. The chicken incorporates a savory element that complements the cream beautifully, ensuring that no single flavor overpowers the others. 
+The balance of these flavors makes each bite satisfying and indulgent, creating a comforting dish that can appeal to a broad range of palates.
+### Aromatic Influences
+The role of garlic and parsley plays a critical part in enhancing the overall flavor profile. Sautéed garlic brings forth its earthy, aromatic qualities, infusing the sauce with warmth and a slight sweetness. Parsley, on the other hand, provides freshness and a mild peppery note that cuts through the richness of the cream, making the dish more refreshing and enjoyable.
+This blend of aromatic influences is what differentiates a straightforward pasta dish from something truly special, inviting diners to savor every bite.
+## Culinary History
+Understanding the background of the dish can enhance appreciation, providing context around its flavors and preparations.
+### Italian Cuisine
+Creamy Garlic Chicken Pasta fits seamlessly into the tapestry of traditional Italian cooking, where pasta dishes are often elevated to sophisticated levels through the use of cream, cheese, and fresh herbs. Italy is known for its regional variations in pasta preparation, many of which highlight simple ingredients prepared with skill and care.
+The use of creamy sauces is particularly popular in various Italian regions, adding to the diversity of flavors and techniques in Italian cooking. Whether it’s fettuccine alfredo or other cream-based dishes, the principles of flavor balance and texture are foundational to what makes Italian cuisine beloved worldwide.
+## Nutritional Information
+Here we delve into the nutritional benefits this dish offers, considering its ingredients and overall composition.
+### Caloric Breakdown
+Each serving of Creamy Garlic Chicken Pasta contains approximately 600 calories. This estimation accounts for the pasta, chicken, heavy cream, and cheese, providing a satisfying, hearty meal. The protein from the chicken supports muscle repair, while the carbohydrates from the pasta fuel energy levels.
+### Potential Modifications
+For those looking to lighten the dish, consider using half-and-half instead of heavy cream or reducing the amount of cheese used. Opting for whole wheat fettuccine can provide more fiber, making the meal more filling without significantly increasing calories. Various vegetable enhancements, such as spinach or broccoli, can boost the nutritional profile without compromising flavor.
+## Conclusion
+Creamy Garlic Chicken Pasta is a rich, flavorsome dish that delights with every bite. With a cooking time of just 30 minutes, it delivers a satisfying meal without fuss, perfect for any weeknight dinner or special occasion. Its creamy texture combined with the savory chicken creates an unforgettable experience that is both comforting and indulgent.
+</t>
+  </si>
+  <si>
+    <t>Spicy Honey Glazed Salmon Recipe: A Quick and Easy Delight</t>
+  </si>
+  <si>
+    <t>Spicy Pesto Pizza: A Flavorful Italian Classic</t>
+  </si>
+  <si>
+    <t>Creamy Garlic Chicken Pasta Recipe</t>
+  </si>
+  <si>
+    <t>{
+  "name": "Spicy Honey Glazed Salmon",
+  "summary": "This Spicy Honey Glazed Salmon features a sweet and spicy glaze that enhances the rich flavor of the salmon. It's a quick and easy dish perfect for any weeknight dinner.",
+  "servings": "4",
+  "prep_time": "10",
+  "cook_time": "15",
+  "total_time": "25",
+  "calories": "350",
+  "course": "Main Course",
+  "cuisine": "Asian",
+  "keywords": [
+    "salmon",
+    "honey",
+    "spicy",
+    "glazed",
+    "easy",
+    "dinner"
+  ],
+  "notes": "Serve with your choice of side dishes for a complete meal. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "4",
+      "unit": "",
+      "name": "salmon fillets"
+    },
+    {
+      "amount": "¼",
+      "unit": "cup",
+      "name": "honey"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "soy sauce"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "sriracha"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "olive oil"
+    },
+    {
+      "amount": "2",
+      "unit": "cloves",
+      "name": "garlic, minced"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "ginger, grated"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Salt and pepper to taste"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Chopped green onions for garnish"
+    }
+  ],
+  "instructions": [
+    "Preheat your oven to 400°F (200°C).",
+    "In a small bowl, whisk together honey, soy sauce, sriracha, olive oil, garlic, and ginger until well combined.",
+    "Season the salmon fillets with salt and pepper on both sides.",
+    "Place the salmon fillets skin-side down on a lined baking sheet.",
+    "Brush the spicy honey glaze generously over the salmon fillets.",
+    "Bake in the preheated oven for 12-15 minutes, or until the salmon flakes easily with a fork.",
+    "Remove from the oven and let it rest for a few minutes.",
+    "Drizzle any remaining glaze over the top and garnish with chopped green onions.",
+    "Serve with your choice of side dishes."
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "name": "Spicy Pesto Pizza",
+  "summary": "This spicy pesto pizza combines the rich flavors of pesto with fresh toppings for a delicious meal. Perfect for pizza lovers looking for a kick.",
+  "servings": "4",
+  "prep_time": "15",
+  "cook_time": "15",
+  "total_time": "30",
+  "calories": "350",
+  "course": "Main Course",
+  "cuisine": "Italian",
+  "keywords": [
+    "pizza",
+    "pesto",
+    "spicy",
+    "Italian",
+    "cheese",
+    "easy"
+  ],
+  "notes": "For extra flavor, use homemade pesto if available. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "1",
+      "unit": "dough",
+      "name": "pizza dough"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "spicy pesto sauce"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "shredded mozzarella cheese"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "sliced cherry tomatoes"
+    },
+    {
+      "amount": "¼",
+      "unit": "cup",
+      "name": "sliced black olives"
+    },
+    {
+      "amount": "¼",
+      "unit": "teaspoon",
+      "name": "red pepper flakes"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Fresh basil leaves for garnish"
+    }
+  ],
+  "instructions": [
+    "Preheat your oven to 475°F (245°C).",
+    "Roll out the pizza dough on a floured surface to your desired thickness.",
+    "Transfer the rolled dough to a pizza stone or baking sheet lined with parchment paper.",
+    "Spread the spicy pesto sauce evenly over the pizza dough.",
+    "Sprinkle the shredded mozzarella cheese on top of the pesto.",
+    "Arrange the sliced cherry tomatoes and black olives over the cheese.",
+    "Sprinkle the red pepper flakes for an extra kick.",
+    "Bake in the preheated oven for 12-15 minutes or until the crust is golden and the cheese is bubbly.",
+    "Remove from the oven and let it cool for a couple of minutes.",
+    "Garnish with fresh basil leaves before slicing.",
+    "Serve hot and enjoy your spicy pesto pizza!"
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "name": "Creamy Garlic Chicken Pasta",
+  "summary": "This creamy garlic chicken pasta is a delicious and comforting dish, perfect for a weeknight dinner. It's made with tender chicken, fettuccine, and a rich garlic cream sauce.",
+  "servings": "4",
+  "prep_time": "10",
+  "cook_time": "20",
+  "total_time": "30",
+  "calories": "600",
+  "course": "Main Course",
+  "cuisine": "Italian",
+  "keywords": [
+    "pasta",
+    "chicken",
+    "creamy",
+    "garlic",
+    "Italian",
+    "dinner",
+    "comfort food"
+  ],
+  "notes": "Adjust seasoning to taste and garnish with fresh parsley for added flavor. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "8",
+      "unit": "oz",
+      "name": "fettuccine pasta"
+    },
+    {
+      "amount": "2",
+      "unit": "",
+      "name": "boneless, skinless chicken breasts"
+    },
+    {
+      "amount": "3",
+      "unit": "tablespoons",
+      "name": "olive oil"
+    },
+    {
+      "amount": "4",
+      "unit": "cloves",
+      "name": "garlic, minced"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "heavy cream"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "grated Parmesan cheese"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Salt and pepper to taste"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Fresh parsley, chopped (for garnish)"
+    }
+  ],
+  "instructions": [
+    "Cook the fettuccine pasta according to package instructions until al dente. Drain and set aside.",
+    "Season the chicken breasts with salt and pepper on both sides.",
+    "In a large skillet, heat the olive oil over medium heat. Add the chicken breasts and cook for about 6-7 minutes on each side, or until fully cooked. Remove from skillet and let rest.",
+    "In the same skillet, add the minced garlic and sauté for about 1 minute until fragrant.",
+    "Pour in the heavy cream and bring to a gentle simmer. Stir in the Parmesan cheese until melted and smooth.",
+    "Slice the cooked chicken into strips and add it to the creamy sauce. Stir to combine.",
+    "Add the cooked fettuccine to the skillet and toss until the pasta is well coated in the sauce.",
+    "Adjust seasoning with additional salt and pepper if needed.",
+    "Serve hot, garnished with chopped fresh parsley."
+  ]
+}</t>
   </si>
 </sst>
 </file>
@@ -487,10 +1048,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C4"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:8">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -500,38 +1061,98 @@
       <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
     </row>
-    <row r="2" spans="1:3">
+    <row r="2" spans="1:8">
       <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C2" t="s">
+        <v>14</v>
+      </c>
+      <c r="D2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F2" t="s">
+        <v>21</v>
+      </c>
+      <c r="G2">
+        <v>1</v>
+      </c>
+      <c r="H2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+      <c r="C3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s">
+        <v>19</v>
+      </c>
+      <c r="F3" t="s">
+        <v>22</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+      <c r="H3" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+      <c r="C4" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s">
+        <v>20</v>
+      </c>
+      <c r="F4" t="s">
+        <v>23</v>
+      </c>
+      <c r="G4">
         <v>3</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3" t="s">
-        <v>4</v>
-      </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C4" t="s">
-        <v>11</v>
+      <c r="H4" t="s">
+        <v>26</v>
       </c>
     </row>
   </sheetData>

--- a/ALL/p11-out/Recipes.xlsx
+++ b/ALL/p11-out/Recipes.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="56" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="156" uniqueCount="138">
   <si>
     <t>Title</t>
   </si>
@@ -34,6 +34,9 @@
     <t>Prompt Image Ingredients</t>
   </si>
   <si>
+    <t>pinterest_image</t>
+  </si>
+  <si>
     <t>main_image</t>
   </si>
   <si>
@@ -76,10 +79,61 @@
     <t>error_ing</t>
   </si>
   <si>
+    <t>Statut Article</t>
+  </si>
+  <si>
+    <t>article</t>
+  </si>
+  <si>
+    <t>article_title</t>
+  </si>
+  <si>
+    <t>id_article</t>
+  </si>
+  <si>
+    <t>pinterest_title</t>
+  </si>
+  <si>
+    <t>recipe_title_pin</t>
+  </si>
+  <si>
+    <t>pinterest_description</t>
+  </si>
+  <si>
+    <t>pinterest_keywords</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_focuskw</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_metadesc</t>
+  </si>
+  <si>
+    <t>_yoast_wpseo_keywordsynonyms</t>
+  </si>
+  <si>
+    <t>category</t>
+  </si>
+  <si>
+    <t>categories</t>
+  </si>
+  <si>
+    <t>status</t>
+  </si>
+  <si>
+    <t>post_url</t>
+  </si>
+  <si>
     <t>Creamy Garlic Parmesan Chicken Pasta</t>
   </si>
   <si>
     <t>The Best Homemade Mac and Cheese</t>
+  </si>
+  <si>
+    <t>Easy 15-Minute Beef Stir Fry</t>
+  </si>
+  <si>
+    <t>Cheesy Loaded Potato Soup</t>
   </si>
   <si>
     <t>Creamy Garlic Parmesan Chicken Pasta 🍝🧄
@@ -145,15 +199,78 @@
 Calories: ~600 per serving</t>
   </si>
   <si>
+    <t>Easy 15-Minute Beef Stir Fry 🍜🥩
+Ingredients:
+- 1 pound beef sirloin, thinly sliced
+- 2 cups mixed bell peppers, sliced
+- 1 cup broccoli florets
+- 3 cloves garlic, minced
+- 2 tablespoons soy sauce
+- 1 tablespoon oyster sauce
+- 1 tablespoon vegetable oil
+- 1 teaspoon sesame oil
+- Cooked rice or noodles, for serving
+Instructions:
+1. Heat the vegetable oil in a large skillet or wok over medium-high heat.
+2. Add the sliced beef to the skillet and cook for about 3-4 minutes, stirring frequently until browned.
+3. Add the minced garlic and cook for an additional minute until fragrant.
+4. Toss in the mixed bell peppers and broccoli florets, stirring well to combine.
+5. Pour the soy sauce and oyster sauce over the stir-fry, mixing everything together thoroughly.
+6. Continue to cook for another 2-3 minutes, or until the vegetables are tender but still crisp.
+7. Drizzle the sesame oil over the stir-fry and give it a final toss.
+8. Serve the beef stir fry over cooked rice or noodles.
+Prep Time: 5 minutes
+Cook Time: 10 minutes
+Total Time: 15 minutes
+Course: Main Dish
+Cuisine: Asian
+Servings: 4
+Calories: ~400 per serving</t>
+  </si>
+  <si>
+    <t>Cheesy Loaded Potato Soup 🥔🧀
+Ingredients:
+- 4 large russet potatoes, peeled and diced
+- 1 medium onion, chopped
+- 3 cloves garlic, minced
+- 4 cups chicken or vegetable broth
+- 1 cup heavy cream
+- 2 cups shredded cheddar cheese
+- 1/2 cup cooked and crumbled bacon
+- 1/4 cup green onions, chopped
+- Salt and pepper to taste
+Instructions:
+1. In a large pot, combine the diced potatoes, chopped onion, minced garlic, and broth. Bring to a boil over medium-high heat.
+2. Reduce heat and let it simmer for about 15-20 minutes, or until the potatoes are tender.
+3. Use an immersion blender to puree the soup until smooth, or transfer in batches to a blender.
+4. Stir in the heavy cream and half of the shredded cheddar cheese until melted and creamy.
+5. Add the crumbled bacon, and season with salt and pepper to taste.
+6. Heat the soup gently until warmed through, then serve in bowls.
+7. Top each bowl with the remaining cheddar cheese and a sprinkle of chopped green onions.
+Prep Time: 10 minutes
+Cook Time: 30 minutes
+Total Time: 40 minutes
+Course: Soup
+Cuisine: American
+Servings: 6
+Calories: ~450 per serving</t>
+  </si>
+  <si>
     <t>2026-05-08 14:43:16</t>
   </si>
   <si>
     <t>2026-05-08 14:43:23</t>
+  </si>
+  <si>
+    <t>2026-05-08 21:36:03</t>
+  </si>
+  <si>
+    <t>2026-05-08 21:36:12</t>
   </si>
   <si>
     <t>{
   "name": "Creamy Garlic Parmesan Chicken Pasta",
-  "summary": "This creamy garlic Parmesan chicken pasta is a delicious and comforting dish that's perfect for any night of the week. It's quick to prepare and packed with flavor.",
+  "summary": "This creamy garlic Parmesan chicken pasta is a delicious and comforting dish, perfect for a quick weeknight dinner. It's rich, flavorful, and sure to please the whole family.",
   "servings": "4",
   "prep_time": "10",
   "cook_time": "20",
@@ -167,10 +284,9 @@
     "creamy",
     "garlic",
     "Parmesan",
-    "Italian",
-    "dinner"
+    "Italian"
   ],
-  "notes": "Garnish with fresh parsley for added flavor and presentation. Calories are per serving.",
+  "notes": "For added flavor, consider using fresh herbs. Calories are per serving.",
   "ingredients": [
     {
       "amount": "8",
@@ -233,7 +349,7 @@
   <si>
     <t>{
   "name": "The Best Homemade Mac and Cheese",
-  "summary": "This creamy and cheesy mac and cheese is a comforting classic that's perfect for any occasion. It's easy to make and sure to please both kids and adults alike.",
+  "summary": "This creamy and cheesy mac and cheese is a comforting classic that's easy to make at home. Perfect for a family dinner or a cozy night in.",
   "servings": "4",
   "prep_time": "10",
   "cook_time": "30",
@@ -243,13 +359,13 @@
   "cuisine": "American",
   "keywords": [
     "mac and cheese",
+    "cheesy",
     "comfort food",
-    "cheesy",
     "pasta",
     "baked",
-    "easy recipe"
+    "homemade"
   ],
-  "notes": "For added crunch, sprinkle breadcrumbs on top before baking. Calories are per serving.",
+  "notes": "For extra crunch, add breadcrumbs on top before baking. Calories are per serving.",
   "ingredients": [
     {
       "amount": "8",
@@ -323,79 +439,869 @@
 }</t>
   </si>
   <si>
-    <t>Realistic, appetizing ULTRA close-up of creamy garlic Parmesan chicken pasta in a clean white ceramic bowl, showcasing the fettuccine coated in a rich, creamy sauce with pieces of diced chicken and a sprinkle of fresh parsley on top. The dish is presented on a light neutral surface, filling 90–100% of the frame, with clear food texture, shallow depth of field, and soft natural daylight casting gentle shadows. The focus is sharp at the center of the food, with a slight 3/4 or eye-level angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-  </si>
-  <si>
-    <t>Realistic, appetizing ULTRA close-up of a creamy, golden baked mac and cheese in a clean white ceramic bowl, showcasing the melted cheese and breadcrumb topping, on a light neutral surface. Tight composition filling 90–100% of frame, clear food texture, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the center of the dish, slight eye-level angle. Exclude people, hands, faces, text, logos, and packaging. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+    <t>{
+  "name": "Easy 15-Minute Beef Stir Fry",
+  "summary": "This quick and flavorful beef stir fry is perfect for a busy weeknight dinner. Ready in just 15 minutes, it's packed with vegetables and delicious sauces.",
+  "servings": "4",
+  "prep_time": "5",
+  "cook_time": "10",
+  "total_time": "15",
+  "calories": "400",
+  "course": "Main Course",
+  "cuisine": "Asian",
+  "keywords": [
+    "beef",
+    "stir fry",
+    "quick",
+    "easy",
+    "vegetables",
+    "15-minute meal"
+  ],
+  "notes": "Serve over rice or noodles for a complete meal. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "1",
+      "unit": "pound",
+      "name": "beef sirloin, thinly sliced"
+    },
+    {
+      "amount": "2",
+      "unit": "cups",
+      "name": "mixed bell peppers, sliced"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "broccoli florets"
+    },
+    {
+      "amount": "3",
+      "unit": "cloves",
+      "name": "garlic, minced"
+    },
+    {
+      "amount": "2",
+      "unit": "tablespoons",
+      "name": "soy sauce"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "oyster sauce"
+    },
+    {
+      "amount": "1",
+      "unit": "tablespoon",
+      "name": "vegetable oil"
+    },
+    {
+      "amount": "1",
+      "unit": "teaspoon",
+      "name": "sesame oil"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Cooked rice or noodles, for serving"
+    }
+  ],
+  "instructions": [
+    "Heat the vegetable oil in a large skillet or wok over medium-high heat.",
+    "Add the sliced beef to the skillet and cook for about 3-4 minutes, stirring frequently until browned.",
+    "Add the minced garlic and cook for an additional minute until fragrant.",
+    "Toss in the mixed bell peppers and broccoli florets, stirring well to combine.",
+    "Pour the soy sauce and oyster sauce over the stir-fry, mixing everything together thoroughly.",
+    "Continue to cook for another 2-3 minutes, or until the vegetables are tender but still crisp.",
+    "Drizzle the sesame oil over the stir-fry and give it a final toss.",
+    "Serve the beef stir fry over cooked rice or noodles."
+  ]
+}</t>
+  </si>
+  <si>
+    <t>{
+  "name": "Cheesy Loaded Potato Soup",
+  "summary": "This creamy and cheesy potato soup is loaded with flavor and topped with bacon and green onions. Perfect for a comforting meal on a chilly day.",
+  "servings": "6",
+  "prep_time": "10",
+  "cook_time": "30",
+  "total_time": "40",
+  "calories": "450",
+  "course": "Soup",
+  "cuisine": "American",
+  "keywords": [
+    "potato soup",
+    "cheesy",
+    "comfort food",
+    "bacon",
+    "easy recipe"
+  ],
+  "notes": "For a thicker soup, blend more of the potatoes. Calories are per serving.",
+  "ingredients": [
+    {
+      "amount": "4",
+      "unit": "large",
+      "name": "russet potatoes, peeled and diced"
+    },
+    {
+      "amount": "1",
+      "unit": "medium",
+      "name": "onion, chopped"
+    },
+    {
+      "amount": "3",
+      "unit": "cloves",
+      "name": "garlic, minced"
+    },
+    {
+      "amount": "4",
+      "unit": "cups",
+      "name": "chicken or vegetable broth"
+    },
+    {
+      "amount": "1",
+      "unit": "cup",
+      "name": "heavy cream"
+    },
+    {
+      "amount": "2",
+      "unit": "cups",
+      "name": "shredded cheddar cheese"
+    },
+    {
+      "amount": "½",
+      "unit": "cup",
+      "name": "cooked and crumbled bacon"
+    },
+    {
+      "amount": "¼",
+      "unit": "cup",
+      "name": "green onions, chopped"
+    },
+    {
+      "amount": "",
+      "unit": "",
+      "name": "Salt and pepper to taste"
+    }
+  ],
+  "instructions": [
+    "In a large pot, combine the diced potatoes, chopped onion, minced garlic, and broth. Bring to a boil over medium-high heat.",
+    "Reduce heat and let it simmer for about 15-20 minutes, or until the potatoes are tender.",
+    "Use an immersion blender to puree the soup until smooth, or transfer in batches to a blender.",
+    "Stir in the heavy cream and half of the shredded cheddar cheese until melted and creamy.",
+    "Add the crumbled bacon, and season with salt and pepper to taste.",
+    "Heat the soup gently until warmed through, then serve in bowls.",
+    "Top each bowl with the remaining cheddar cheese and a sprinkle of chopped green onions."
+  ]
+}</t>
+  </si>
+  <si>
+    <t>Realistic, appetizing ULTRA close-up of creamy garlic Parmesan chicken pasta served in a clean white ceramic bowl, on a light neutral surface. The dish features fettuccine pasta coated in a rich, creamy sauce, with diced chicken pieces and a sprinkle of fresh parsley on top. The composition fills 90–100% of the frame, showcasing the texture of the pasta and sauce, with a shallow depth of field, soft natural daylight, and gentle shadows. Sharp focus at the center of the food, captured from a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>Realistic, appetizing ULTRA close-up of a creamy, baked mac and cheese dish, featuring a golden, bubbly top with crispy breadcrumbs, served in a clean white ceramic bowl on a light neutral surface. The composition fills 90–100% of the frame, showcasing the rich texture of the melted cheeses and pasta, with a shallow depth of field and soft natural daylight creating gentle shadows. The focus is sharp at the center of the dish, presented at a slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>Realistic, appetizing ULTRA close-up of a vibrant beef stir fry featuring thinly sliced beef sirloin, colorful mixed bell peppers, and fresh broccoli florets, all glistening with soy and oyster sauce in a clean white ceramic bowl. The dish is garnished with a drizzle of sesame oil, served on a light neutral surface. Tight composition filling 90–100% of frame, showcasing clear food texture, shallow depth of field, soft natural daylight, and gentle shadows. Sharp focus at the food center, slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>Realistic, appetizing ULTRA close-up of a creamy cheesy loaded potato soup served in a clean white ceramic bowl, topped with shredded cheddar cheese and chopped green onions, on a light neutral surface. Tight composition filling 90–100% of frame, showcasing the smooth texture of the soup and the vibrant toppings, shallow depth of field, soft natural daylight, gentle shadows. Sharp focus at the center of the soup, slight 3/4 angle. , food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
   </si>
   <si>
     <t>fettuccine pasta, olive oil, chicken breasts, garlic, heavy cream, Parmesan cheese, Italian seasoning, salt, pepper, parsley, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
   </si>
   <si>
-    <t>elbow macaroni, cheddar cheese, mozzarella cheese, Parmesan cheese, butter, flour, milk, garlic powder, onion powder, salt, pepper, breadcrumbs, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0508134/9ecb2fa66aa.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0508140/3b2107ebcf7.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/5ab8c013f95.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508140/149ec4eb310.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/733c5fbdd0b.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508140/cdd3adb2baf.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/3eac6f8cd24.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508140/841c9483046.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508134/9fc58a06c24.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0508140/327bf652331.png</t>
+    <t>elbow macaroni, sharp cheddar cheese, mozzarella cheese, Parmesan cheese, butter, all-purpose flour, milk, garlic powder, onion powder, salt, pepper, breadcrumbs, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>beef, bell peppers, broccoli, garlic, soy sauce, oyster sauce, vegetable oil, sesame oil, rice, noodles, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>potatoes, onion, garlic, broth, cream, cheese, bacon, green onions, salt, pepper, ingredients-only, top-down flat lay, each ingredient appears once, neatly separated in small bowls and directly on the surface, wide framing with generous margins, clean spacing, light neutral background (soft gray or light beige) with subtle texture (stone or light wood), soft natural daylight, soft minimal shadows, -- no text, -- no labels, -- no logos, -- no packaging, -- minimal styling, food-only scene, dish-focused, exclude people, exclude hands, exclude faces, no text, no labels, no logos, no packaging, kitchen or neutral surface only --v 6.1</t>
+  </si>
+  <si>
+    <t>C:\Users\leno\Documents\GitHub\PINTEREST\ALL\p11-out\output_images\image_1.jpg</t>
+  </si>
+  <si>
+    <t>C:\Users\leno\Documents\GitHub\PINTEREST\ALL\p11-out\output_images\image_2.jpg</t>
+  </si>
+  <si>
+    <t>C:\Users\leno\Documents\GitHub\PINTEREST\ALL\p11-out\output_images\image_3.jpg</t>
+  </si>
+  <si>
+    <t>C:\Users\leno\Documents\GitHub\PINTEREST\ALL\p11-out\output_images\image_4.jpg</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0509083/4c6d18e42f7.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0509083/b23511f9b46.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0509083/b19d0e3b964.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/main/j0509083/bfe66b55de0.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/4bb48326fbf.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/c71a9490822.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/2f614df4950.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/916f884124f.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/39d3ac025f9.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/c29a60ab578.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/ff16811c40f.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/28b9bcad928.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/f031b1f9ba4.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/3bd740de6ce.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/427f7d2ef37.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/77f9eea423b.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/72678604152.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/28c2bb54c33.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/8557643edc8.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/main/j0509083/44911653493.png</t>
   </si>
   <si>
     <t>DONE</t>
   </si>
   <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0508140/e8c19b41e9b.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0508140/f090e22fb19.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/c295164eb73.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/70b9f79600b.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/f8c11015625.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/c425e9ff4cf.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/92c13bcb460.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/bb8b9edf865.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/835af1ea604.png</t>
-  </si>
-  <si>
-    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0508140/f013e725002.png</t>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0509083/e4a24c6f257.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0509083/6a0bc1615db.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0509083/3d137db2778.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_grids/ingredients/j0509083/95c57db0b69.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/ea4d53261df.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/1f17c35f2aa.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/447149f8b79.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/7c89944ab21.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/d27d7c0dab0.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/035c1723a67.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/6788d0594ca.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/ecc40b15896.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/e11ec41da4b.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/d655e27d205.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/51b2b50ea40.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/fe1e38dbcc1.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/e57828263e2.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/0c91dae905b.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/303d520b2b5.png</t>
+  </si>
+  <si>
+    <t>https://pub-265e755dc4334724956a9d45d1c8bfb0.r2.dev/midjourney_splits/ingredients/j0509083/4cd9e84c88e.png</t>
+  </si>
+  <si>
+    <t>DONE ARTICLE</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Creamy Garlic Parmesan Chicken Pasta
+## Introduction
+Creamy Garlic Parmesan Chicken Pasta offers a delightful blend of flavors and textures, perfect for any dinner table. This Italian-inspired dish brings together succulent chicken and smooth, rich cream to create a meal that is both comforting and satisfying. The addition of fettuccine pasta ensures that every forkful is infused with a creamy essence, making it a favorite among pasta lovers. Whether you're planning a family dinner or a cozy date night, this dish is sure to impress with its elegance and ease of preparation.
+In just 30 minutes, you can prepare a dish that feels indulgent without the fuss of lengthy cooking techniques. The creamy sauce coats the fettuccine perfectly, turning the humble pasta into a luxurious meal. Ideal for busy weeknights, it can also serve as a crowd-pleaser at gatherings, ensuring everyone leaves the table happy and satisfied. 
+The combination of garlic and Parmesan in the sauce adds depth and richness, transforming simple ingredients into a restaurant-quality experience. Serve this dish alongside some crusty garlic bread or a fresh garden salad to complement the meal beautifully, elevating your dining experience even further.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 20 minutes
+- Total Time: 30 minutes
+- Course: Main Course
+- Cuisine: Italian
+- Servings: 4
+- Calories: ~540 per serving
+## Ingredients
+- 8 oz fettuccine pasta
+- 2 tablespoons olive oil
+- 2 boneless, skinless chicken breasts, diced
+- 4 cloves garlic, minced
+- 1 cup heavy cream
+- 1 cup grated Parmesan cheese
+- 1 teaspoon Italian seasoning
+- Salt and pepper to taste
+- Fresh parsley, chopped (for garnish)
+{{image_ing_1}}
+## Instructions
+1. Cook the fettuccine pasta according to package instructions until al dente. Drain and set aside.
+2. In a large skillet, heat the olive oil over medium heat. Add the diced chicken and season with salt and pepper. Cook until browned and cooked through, about 5-7 minutes.
+3. Add the minced garlic to the skillet and sauté for another 1-2 minutes until fragrant.
+4. Pour in the heavy cream and bring to a simmer. Reduce heat to low and stir in the Parmesan cheese until melted and smooth.
+5. Mix in the Italian seasoning and adjust seasoning with more salt and pepper if needed.
+6. Add the cooked fettuccine to the skillet and toss to combine, ensuring the pasta is well coated with the creamy sauce.
+7. Remove from heat and garnish with chopped parsley before serving.
+8. Enjoy your creamy garlic Parmesan chicken pasta!
+## Preparing the Pasta
+To kick off your culinary adventure with Creamy Garlic Parmesan Chicken Pasta, preparing the fettuccine correctly is crucial. Begin by bringing a large pot of salted water to a rolling boil. This step ensures that your pasta cooks evenly and absorbs the necessary flavor as it cooks. 
+### Cooking Time
+Follow the package instructions for cooking the fettuccine until it reaches the ideal al dente texture. Al dente pasta maintains a firm bite, which is perfect for soaking up the creamy sauce without becoming mushy.
+### Draining and Setting Aside
+Once the pasta is cooked, carefully drain it in a colander. It's essential to ensure that you retain some of the pasta cooking water; this can be useful if you want to adjust the consistency of your sauce later. Setting the drained fettuccine aside allows you to focus on preparing the protein and sauce without the pasta sticking together.
+### Preventing Sticking
+After draining, toss the fettuccine with a dash of olive oil if desired. This simple technique prevents the pasta from clumping together and ensures that each strand stays separated, ready to mingle with the rich sauce later.
+## Cooking the Chicken
+The chicken is a star component of this dish, contributing protein and flavor. Selecting the right chicken is essential for achieving the desired result and ensuring a perfect balance of textures.
+### Choosing the Right Chicken
+For this recipe, boneless, skinless chicken breasts are ideal. They cook quickly and evenly, making them a practical choice for weeknight dinners. Their mild flavor acts as the perfect canvas to absorb the delicious sauce you’ll create.
+### Seasoning Techniques
+As you prepare to cook the diced chicken, season it generously with salt and pepper. This step may seem simple, but it enhances the chicken's natural flavor, helping it shine in the overall dish.
+### Cooking Method
+In a large skillet, heat the olive oil over medium heat. Once hot, add the seasoned chicken to the pan. Aim for a cooking time of about 5-7 minutes, turning the pieces to achieve a golden-brown exterior while ensuring they remain moist and tender inside. The goal is to have the chicken cooked through, with a delightful crust that adds to the overall texture of your pasta dish.
+## Sautéing the Garlic
+To elevate your Creamy Garlic Parmesan Chicken Pasta, incorporating garlic into the dish is crucial. Garlic not only adds a wonderful aromatic quality but also enhances the flavor profile significantly.
+### Fresh vs. Pre-minced Garlic
+Opting for fresh garlic instead of pre-minced alternatives can make a considerable difference in taste. Fresh garlic provides a vibrant flavor that infuses the dish with an authentic taste you simply can't duplicate.
+### Sautéing Techniques
+As the chicken nears completion, add the minced garlic to the skillet. It's essential to sauté it over medium heat, stirring constantly to avoid burning. Garlic cooks quickly, and burnt garlic can introduce a bitter taste that may overshadow the beautiful creamy sauce you are about to create. 
+### Timing for Optimal Taste
+For the best flavor, sauté the garlic for about 1-2 minutes until it's fragrant. This indicates that it's done and ready to move on to the next step of creating your luscious cream sauce.
+## Creating the Cream Sauce
+The centerpiece of this recipe is the creamy sauce that ties everything together. A well-prepared cream sauce elevates the dish to a restaurant-quality standard, adding richness and depth.
+### Combining the Cream and Parmesan
+Once your garlic has reached the perfect level of fragrance, pour in the heavy cream. Allow it to come to a gentle simmer before reducing the heat to low. Gradually stir in the grated Parmesan cheese, ensuring it melts smoothly into the cream, creating a luscious, velvety sauce. The combination of the cream and cheese adds an indulgent richness that blends perfectly with the chicken and pasta, ensuring each bite is a delight.
+This initial phase sets the stage for a truly delicious meal that emphasizes the beauty of simple ingredients coming together to create something special. In the next section, we'll continue exploring how to finish assembling your Creamy Garlic Parmesan Chicken Pasta, making sure every element is perfectly balanced for the most delectable results.
+Techniques for Mixing Heavy Cream and Parmesan Cheese to Create a Smooth Sauce
+Creating a velvety sauce is at the heart of any successful creamy pasta dish, and the technique applied when mixing heavy cream and Parmesan cheese can significantly impact the outcome. Start by ensuring your heavy cream is at room temperature before adding it to the skillet; this helps to minimize shocking the ingredients and aids in smoother integration.
+As you pour in the heavy cream, do so gradually while stirring continuously. This technique allows the cream to blend seamlessly with the sauteed garlic and chicken, preventing lumps from forming. Once the heavy cream is incorporated well, sprinkle the grated Parmesan cheese into the mixture bit by bit rather than all at once. This gradual addition helps the cheese melt evenly, resulting in that signature creamy texture. Use a wooden spoon or a whisk for the best results when mixing, as they are effective in breaking down any clumps and creating uniform consistency.
+### Simmering to Perfection
+Simmering is crucial in developing the flavors and texture of the sauce. After fully incorporating the heavy cream and Parmesan, bring the mixture to a gentle simmer over low heat. A good rule of thumb is to maintain a temperature just below the boiling point; this allows the cheese to melt and blend into the sauce without separating or curdling. 
+For the best results, allow the sauce to simmer for at least 3-5 minutes. This permits the flavors to meld beautifully while thickening the sauce slightly, creating a luxurious coating for your pasta. Continuous stirring during this process is essential, as it ensures that no ingredients settle and burn at the bottom, and it promotes even heat distribution throughout the sauce.
+### Adjusting Flavor Profiles
+Taste-testing and adjusting the seasoning throughout the cooking process is vital for achieving the desired flavor. Salt and pepper are essential seasonings, but aromatics like Italian seasoning also elevate the dish. Once the cream and cheese have combined and the sauce has simmered for a few minutes, taste it to assess the seasoning. 
+Should the sauce taste a bit bland, consider adding a pinch more salt or seasoning. If you're aiming for a brighter flavor profile, a dash of lemon juice can enhance the overall taste without altering the creamy essence. Remember, it’s much easier to add more seasoning gradually than to attempt to counteract an overly seasoned dish.
+## The Final Dish: Combining Ingredients
+Once your sauce is ready and seasoned to perfection, it's time to bring all the components of the dish together. The fettuccine pasta, which should be cooked al dente, will be the final element to join the creamy sauce.
+### Tossing the Pasta
+When combining the pasta with your sauce, an effective method involves using tongs or a large serving fork to toss the fettuccine gently with the sauce. This action allows every single strand of pasta to be coated in the rich, creamy sauce, ensuring that every bite is full of flavor. Tossing rather than stirring vigorously helps to avoid breaking the pasta strands while evenly distributing the sauce throughout.
+### Timing for Mixing
+To achieve the best results, it's essential to mix the pasta with the sauce right before serving. If the sauce sits for too long after preparation, it can thicken excessively or lose some of its creamy qualities. Having your pasta cooked and drained just before your sauce is fully prepared allows you to mix them seamlessly for maximum freshness and flavor.
+### Presentation Tips
+The final presentation of your Creamy Garlic Parmesan Chicken Pasta is critical to create an inviting dining experience. When plating, start by twirling a mound of pasta on each plate for an elegant look. Ensuring that the sauce clings to the pasta will give it a glossy appearance. A sprinkle of additional Parmesan cheese on top adds a nice visual element, as does a light touch of fresh parsley.
+To elevate the aesthetic further, consider using a platter to serve a family-style dish. Incorporate some extra garnishes like cracked pepper or a light drizzle of olive oil for an added gourmet touch.
+## Garnishing Your Pasta
+Adding a finishing garnish can enhance the presentation of your Creamy Garlic Parmesan Chicken Pasta while introducing another layer of flavor.
+### Choosing the Right Parsley
+Fresh parsley is the recommended garnish for this dish, as its bright green color adds vibrance and its fresh flavor complements the creaminess of the pasta. When selecting parsley, look for bright, perky leaves without any signs of wilting or discoloration. Flat-leaf parsley typically has a more robust flavor, whereas curly parsley is more decorative but may have a milder taste.
+### Proper Garnishing Techniques
+To achieve an appealing garnish, chop the parsley finely and sprinkle it evenly over the pasta just before serving. This method ensures that every plate gets an equal share of this fresh herb without overpowering the dish. A few whole leaves can also be placed on each serving as a decorative touch.
+### Complementary Garnishes
+While parsley is a classic choice, there are other garnishes that could elevate your dish further. Consider adding a drizzle of balsamic reduction for a tangy and slightly sweet contrast or a topping of crushed red pepper flakes if you're seeking a bit of heat. Additionally, thinly sliced or diced cherry tomatoes can provide a burst of color and a refreshing flavor.
+## Nutritional Information
+Understanding the nutritional aspects of Creamy Garlic Parmesan Chicken Pasta can aid in meal planning and dietary considerations.
+### Caloric Breakdown
+Each serving of this creamy dish contains approximately 540 calories. This caloric content is primarily derived from the heavy cream and Parmesan cheese, which contribute to its rich flavor and texture.
+### Nutritional Benefits
+The dish offers a mix of macronutrients, including protein from the chicken and some carbohydrates from the fettuccine pasta. However, due to the heavy cream, it is higher in fat content, primarily from saturated fats. When planned properly, this dish can offer a satisfying experience while still remaining a balanced option when paired with lighter side dishes.
+### Balancing Meals
+To maintain a well-rounded diet, consider serving this pasta alongside a fresh salad or steamed vegetables. Incorporating greens on the side can help offset the richness of the pasta, providing essential vitamins and minerals without overwhelming the palate.
+## Storing Leftovers
+After enjoying your Creamy Garlic Parmesan Chicken Pasta, it’s essential to know how to store leftover portions properly to maintain the quality and flavor.
+### Best Storage Practices
+To store any leftovers, use airtight containers. This type of storage helps keep the dish fresh and prevents it from absorbing any unwanted odors from the fridge. Let the pasta cool to room temperature before sealing it to prevent condensation from forming inside the container.
+### Reheating Suggestions
+The best methods for reheating this dish are using either the stovetop or a microwave. For stovetop reheating, add a splash of milk or cream while gently warming it on low heat, stirring frequently to maintain creaminess. For microwave reheating, use short intervals at medium power and stir occasionally to ensure even heating.
+### Shelf Life
+Generally, leftovers can be kept in the refrigerator for up to 3 days. If you want to preserve them for a longer period, consider freezing the pasta. Be aware that while it will retain its flavor, the texture may change slightly upon thawing.
+## Variations and Substitutions
+For those looking to customize the Creamy Garlic Parmesan Chicken Pasta recipe, several variations and ingredient substitutions can enhance its versatility.
+### Protein Alternatives
+If you're seeking a different protein source, consider substituting the chicken with shrimp or sautéed vegetables for a vegetarian option. Tofu or seitan can provide similar satisfaction while retaining the dish’s creamy texture.
+### Pasta Options
+While fettuccine creates a lovely base for the sauce, alternative pasta shapes such as penne or even whole-grain spaghetti can be used depending on preference or dietary needs.
+### Dietary Modifications
+For those with dietary restrictions, lactose-free cream and cheese can seamlessly replace traditional dairy products, allowing everyone to enjoy this dish. Gluten-free pasta options are also widely available and can provide a similar taste and texture without the gluten content.
+## Conclusion
+Creamy Garlic Parmesan Chicken Pasta combines rich flavors and creamy texture, making it a satisfying main course. With a quick preparation time of just 30 minutes, it offers an easy dining option without compromising on taste. A perfect choice for both casual dinners or special occasions, this dish promises to please any palate.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># The Best Homemade Mac and Cheese Recipe
+## Introduction
+Mac and cheese is the quintessential comfort food, evoking feelings of nostalgia and warmth. This dish is beloved by both children and adults alike, often savored during cozy family gatherings or as a fulfilling solo meal during a quiet evening at home. Its creamy, cheesy goodness seeps into the heart of every food lover, making it an enduring favorite that transcends generations.
+Historically, mac and cheese has fascinating origins, with variations popping up around the world. It is traditionally believed to have roots in Italy, where pasta and cheese were combined in the 1700s. Over time, different cultures adopted and adapted the concept, leading to unique twists that feature local ingredients and flavors. In the United States, mac and cheese has become a staple, especially in Southern cuisine, where it holds a place of honor on many tables.
+While store-bought options are convenient, nothing matches the delightful experience of crafting your own homemade version. Homemade mac and cheese allows you to control the quality of ingredients and customize flavors, resulting in a dish that's often richer and more satisfying than anything you can find pre-packaged in the grocery aisle. This recipe promises to deliver a luxurious cheesy experience that is both quick and easy to prepare.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 30 minutes
+- Total Time: 40 minutes
+- Course: Main Course
+- Cuisine: American
+- Servings: 4
+- Calories: ~600 per serving
+## Ingredients
+- 8 ounces elbow macaroni
+- 2 cups sharp cheddar cheese, shredded
+- 1 cup mozzarella cheese, shredded
+- 1/2 cup grated Parmesan cheese
+- 3 tablespoons butter
+- 3 tablespoons all-purpose flour
+- 2 cups milk
+- 1/2 teaspoon garlic powder
+- 1/2 teaspoon onion powder
+- Salt and pepper to taste
+- 1/2 cup breadcrumbs (optional for topping)
+Every ingredient plays a crucial role in achieving the perfect cheese sauce for your mac and cheese. The elbow macaroni serves as the comforting base, while the combination of sharp cheddar, mozzarella, and Parmesan creates a rich tapestry of flavor and texture that is both creamy and cheesy. The butter and flour mix to create a roux, which is essential for the sauce's thickness. Milk is key for the creamy consistency, and the garlic and onion powders provide subtle undertones that enhance the dish without overpowering it. Finally, the breadcrumbs (if you choose to add them) create a lovely crunchy topping that contrasts beautifully with the soft, cheesy macaroni beneath.
+Choosing high-quality cheese is vital for the best flavor. When selecting your cheddar, look for a sharp variety that offers a robust taste. Mozzarella adds a stretchiness that is typical of classic mac and cheese, while Parmesan introduces a nutty depth that rounds out the flavors beautifully. For the macaroni, any brand of elbow pasta will do, but opting for a high-quality artisanal pasta can elevate your dish even further.
+{{image_ing_1}}
+## Preparation Tips
+Before diving into making this creamy mac and cheese, gathering and preparing your ingredients is essential. Prepping your ingredients ahead of time ensures a smoother cooking process and helps prevent any last-minute scrambles.
+Start by shredding the cheeses, particularly the cheddar and mozzarella, if they aren’t pre-shredded. Freshly shredded cheese melts more effectively because it doesn't contain anti-caking agents that can inhibit melting. Measure out the flour and seasonings in advance, as having everything at hand will keep you organized and allow you to focus on the cooking process without interruptions. 
+Additionally, keep your cooking space tidy and organized. Clear off any unnecessary items and have your pots and pans ready. This ensures that you can easily access everything you need when it's time to start cooking.
+## Cooking the Pasta
+Cooking the elbow macaroni correctly is an essential step in achieving perfect mac and cheese. Follow the package instructions closely to cook the pasta al dente, which means it should be tender but still firm when bitten. This texture is crucial because the pasta will continue to cook in the oven, and you want to avoid overly soft noodles that can become mushy.
+Begin by bringing a large pot of salted water to a vigorous boil. The salt will season the pasta as it cooks, enhancing the overall flavor of your dish. Once boiling, add the elbow macaroni and stir occasionally to prevent sticking. After cooking the pasta for the recommended time, taste a piece to ensure it’s al dente before draining it in a colander. Make sure to shake off any excess water and set it aside; this helps ensure that it doesn't become watery when combined with the cheese sauce.
+## Making the Cheese Sauce
+Creating the cheese sauce is the heart of this mac and cheese recipe. Start by melting butter in a large saucepan over medium heat, allowing it to bubble gently without browning. Once melted, whisk in the all-purpose flour to create a roux. This mixture acts as a thickening agent for your sauce and should be cooked for about a minute until it becomes bubbly but not too dark in color.
+Next, gradually add the milk while continuously whisking. This will help prevent lumps from forming in your sauce. Continue to whisk as the mixture bubbles and thickens, reaching a creamy consistency. Once thickened, incorporate the garlic powder, onion powder, salt, and pepper, stirring to combine all those flavors seamlessly.
+Once your sauce is well-seasoned and thick, remove it from the heat and mix in the shredded cheddar, mozzarella, and Parmesan cheese. Stir until the cheeses have melted completely, producing a smooth and creamy sauce. 
+Once the cheese sauce reaches its desired consistency, you can proceed to mix in the cooked macaroni, ensuring every piece is thoroughly coated with that rich and luxurious sauce, preparing your mac and cheese for the oven. 
+This foundational cheese sauce, combined with the perfectly cooked elbow macaroni, sets the stage for a mac and cheese experience that's not just good, but the best homemade version you can make.
+## Explanation of the Cooking Process for Flour and Butter
+Creating the base for your mac and cheese begins with the important step of making a roux, which is a mixture of flour and fat—in this case, butter. The process starts by melting the butter in a large saucepan over medium heat. This step is crucial, as the butter must be hot enough to integrate with the flour without burning. Once the butter has melted completely, add the all-purpose flour while continuously whisking. 
+It is essential to cook the roux for about a minute; this helps remove the raw flour taste and begins to develop a nutty aroma. The mixture will become slightly foamy as it cooks, which is a good indication that the roux is properly formed. If you skip this step or do not cook the roux long enough, you risk having a grainy texture in your final product.
+## Gradual Incorporation of Milk
+Once the roux is prepared, the next step is to incorporate the milk gradually. This is a vital process as adding the milk too quickly can create lumps in your cheese sauce. Pour in the milk slowly, whisking continuously to ensure that the roux melds perfectly with the liquid. As the mixture heats up, it will start to thicken. Keep whisking until you see bubbles breaking the surface, indicating that the sauce is almost at the desired consistency. 
+## Techniques for Achieving the Right Consistency
+The goal here is to achieve a velvety, smooth cheese sauce that will cloak the macaroni beautifully. When the sauce thickens sufficiently—usually after a few minutes of continuous whisking—you'll know it is ready once it coats the back of a spoon. If your sauce seems too thick, you may add a bit more milk until the desired creaminess is reached. Conversely, if it appears too runny, continue simmering while whisking until it thickens further. 
+## Adding Spices for Flavor Enhancement
+The spices used in the cheese sauce, such as garlic powder and onion powder, play a significant role in enhancing the overall flavor profile of your mac and cheese. After removing the thickened sauce from heat, adding these spices brings warmth and depth to the dish. Simply stir them in along with the salt and pepper to taste. It’s a good practice to start with small amounts, as the flavors will meld together during the cooking process, and you can always adjust to your preference.
+## Combining Ingredients
+### Best Practices for Mixing Pasta with Cheese Sauce
+Once your cheese sauce is ready, it’s time to bring the components together. Begin by combining the cooked elbow macaroni with the cheese sauce in a large mixing bowl. It’s advisable to do this while both the pasta and sauce are still warm, as it helps the cheese cling better to the pasta, creating that creamy texture you desire.
+### Ensuring Even Coating of Macaroni
+To ensure every piece of pasta is well-coated with the cheese sauce, gently fold the macaroni and sauce together rather than stirring vigorously. This prevents the pasta from breaking apart while ensuring the sauce envelops each elbow noodle evenly.
+### Tips for Adjusting Consistency If Needed
+If you find the sauce too thick during the mixing process, a splash of reserved pasta cooking water or a little extra milk can be added to loosen it up. Start with a small amount and adjust until you reach the desired creaminess. 
+## Preparing for Baking
+### Instructions for Transferring Mac and Cheese to a Baking Dish
+After combining the macaroni and cheese sauce, the next step is to transfer this delightful mixture to a greased baking dish. A 9x13-inch baking dish works well for this recipe, providing ample space for even baking. 
+### Strategies for Greasing the Dish
+Greasing your baking dish is essential to prevent sticking. You can achieve this by applying a thin layer of butter or a non-stick cooking spray to the bottom and sides of the dish, ensuring a smooth release when serving.
+### Options for Including Breadcrumbs for Texture
+For an added layer of texture and flavor, you may choose to sprinkle breadcrumbs on top before baking. This not only provides a delightful crunch but also an appealing golden finish.
+### Benefits of Using Breadcrumbs and Alternatives
+Breadcrumbs can be customized as well; panko breadcrumbs create a lighter, airier topping, while crushed crackers or cornflakes can also be used for an alternative texture. Each option adds a unique element to your mac and cheese.
+## Baking Process
+### Explanation of the Baking Step
+Baking the mac and cheese is where the magic truly happens. Once your dish is assembled, place it in the preheated oven set to 350°F (175°C). This optimal temperature allows the cheese to melt and the macaroni to absorb flavors, culminating in a rich and creamy dish.
+### Importance of Temperature and Timing
+Bake the mac and cheese for 20-25 minutes. Keeping an eye on the dish is essential; an accurate oven temperature is key to achieving that bubbly, golden top, which indicates it’s ready to serve. 
+### Visual Indicators for Doneness (Golden and Bubbly)
+You’ll know your mac and cheese is done when the top is golden brown, and small bubbles are forming along the edges. If, in the last few minutes, the top isn’t browning as expected, a quick broil can help achieve that perfect finish. 
+## Cooling and Serving
+### Recommended Cooling Time Before Serving
+After removing your mac and cheese from the oven, allowing it to cool for a few minutes is important. This helps the dish set slightly and makes serving easier. A cooling time of about 5-10 minutes should suffice.
+### Suggestions for Garnishing or Enhancing Presentation
+For an impressive presentation, you can add a sprinkle of extra grated cheese, fresh herbs like parsley, or even a dash of paprika for color right before serving. 
+### Pairing Suggestions with Side Dishes or Beverages
+This mac and cheese pairs wonderfully with a refreshing side salad or steamed vegetables. An ice-cold drink, such as lemonade or iced tea, can balance the richness of this hearty dish.
+## Variations and Add-ins
+### Ideas for Customizing the Mac and Cheese
+While the classic recipe is delightful on its own, customizing your mac and cheese can add a unique flair. Consider adding sautéed vegetables such as broccoli, spinach, or mushrooms for a nutritional boost.
+### Vegetables, Meats, and Other Cheese Options
+For those who enjoy meats, diced cooked bacon or chicken can enhance the savory flavor profile. Experimenting with different cheese varieties, such as pepper jack or gouda, can also yield delicious results.
+### Healthier Alternatives and Adjustments for Dietary Preferences
+If you’re looking to make your mac and cheese healthier, consider using whole wheat pasta or adding pureed vegetables to the cheese sauce for extra nutrition without compromising flavor.
+## Storing and Reheating
+### Best Practices for Storing Leftovers
+Once you’ve enjoyed your homemade mac and cheese, any leftovers can be stored in an airtight container. Make sure to cool the dish completely before sealing it to prevent moisture buildup.
+### Containers and Refrigeration Tips
+Use a container that fits the amount of leftover mac and cheese snugly without too much airspace. Refrigeration is key; it helps keep the flavors fresh and the dish safe to eat.
+### Methods for Reheating to Retain Texture and Flavor
+To reheat, a microwave or oven can be used. If using a microwave, adding a splash of milk will help retain creaminess. When using an oven, cover your dish with foil to keep moisture in, reheating at 350°F (175°C) until warmed through.
+## Nutritional Information
+### Breakdown of Nutritional Aspects
+This delicious mac and cheese has approximately 600 calories per serving. It strikes a good balance between indulgence and satisfaction, providing a comforting meal that's perfect for various occasions.
+### Focus on Calorie Count and Serving Size
+With the serving size of 4, it makes for a convenient meal for family dinners or gatherings. The calorie count allows you to enjoy this dish while managing portions effectively.
+### Discussion on How to Make the Dish More Wholesome
+To make this dish more wholesome, consider incorporating more vegetables or opting for reduced-fat cheeses. These small adjustments can contribute to a healthier meal while still allowing you to indulge in the beloved cheesy goodness.
+## Conclusion
+The Best Homemade Mac and Cheese delivers a perfect blend of cheesy goodness and creamy texture in each bite. With a total time of just 40 minutes, it easily serves four, making it an ideal main course for families or gatherings. Enjoy this comforting dish that highlights classic American cuisine in a delightful homemade version.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Easy 15-Minute Beef Stir Fry
+## Introduction
+In the fast-paced world we live in today, finding time to prepare a nutritious meal can be quite the challenge. This is where quick and delicious dishes like the Easy 15-Minute Beef Stir Fry shine. Perfect for busy weeknights, this recipe allows you to whip up a satisfying main dish that is both flavorful and strikingly colorful. With a combination of tender beef and vibrant, fresh vegetables, it's an embodiment of the bright and exciting flavors typical of Asian cuisine.
+Stir-fried dishes have long held a special place in the hearts of many. They are not only a quick solution for dinner but also a fantastic way to pack in a variety of nutrients. The incorporation of lean beef and a rainbow of vegetables provides a nutritious meal that can cater to health-conscious diners. The textures of the crispy vegetables combined with the savory beef, all brought together by a savory sauce, are enough to entice anyone at your dinner table.
+Whether you are a seasoned home cook or someone just finding your footing in the kitchen, this recipe promises to be a breeze. It’s not just about whipping up a meal; it's about creating comfort food that can be enjoyed by the whole family.
+## Recipe Overview
+- Prep Time: 5 minutes
+- Cook Time: 10 minutes
+- Total Time: 15 minutes
+- Course: Main Dish
+- Cuisine: Asian
+- Servings: 4
+- Calories: ~400 per serving
+This Easy 15-Minute Beef Stir Fry is designed for simplicity without sacrificing flavor. With just 5 minutes of prep and 10 minutes of cooking, you will have a delicious meal on the table in a flash. It is an ideal dish for both novice cooks and those who can whip up meals with their eyes closed, as it combines straightforward techniques with accessible ingredients for a universally appealing dish. If you’re craving something hearty yet quick, look no further than this beef stir fry recipe!
+## Ingredients
+- 1 pound beef sirloin, thinly sliced
+- 2 cups mixed bell peppers, sliced
+- 1 cup broccoli florets
+- 3 cloves garlic, minced
+- 2 tablespoons soy sauce
+- 1 tablespoon oyster sauce
+- 1 tablespoon vegetable oil
+- 1 teaspoon sesame oil
+- Cooked rice or noodles, for serving
+Crafting your Easy 15-Minute Beef Stir Fry requires only a handful of ingredients, each adding its unique flair to the dish. The star of the show, beef sirloin, is not only tender but also absorbs the flavors beautifully. Mixed bell peppers, with their delightful crunch and sweetness, along with broccoli, contribute both color and nutrients. Garlic is included for a punch of flavor that cannot be overlooked. The addition of soy and oyster sauce gives the stir fry that classic savory note, while the sesame oil adds a hint of nutty richness. Served over rice or noodles, this dish is not just a meal; it’s an experience filled with contrasting textures and harmonious flavors.
+{{image_ing_1}}
+## Cooking Equipment
+To make the Easy 15-Minute Beef Stir Fry, you’ll need some essential kitchen tools that will simplify the process:
+- Skillet or Wok: A large skillet or a wok is crucial for achieving that high heat needed for stir-frying while allowing flexibility in movement.
+- Cutting Board: A sturdy cutting board will provide a stable surface for your preparation.
+- Sharp Knife: A good, sharp knife is a necessity for easily slicing the beef and vegetables.
+- Measuring Spoons: For precise measurements of sauces and oils, measuring spoons are essential.
+- Spoon or Spatula for Stirring: A spatula or a sturdy spoon will be necessary for tossing your ingredients and ensuring they cook evenly.
+These few tools are all you need to create this flavorful dish quickly and efficiently, making your cooking experience both enjoyable and effective.
+## Preparation Steps
+Preparation is key to the success of your stir fry, and each step plays an important role in ensuring that everything cooks evenly and tastes great.
+Slicing the Beef: The first step involves slicing one pound of beef sirloin thinly. A sharp knife works wonders here, and it's helpful to have the beef slightly frozen for easier handling. Aim for uniform slices to ensure that the beef cooks evenly during the stir-frying process. 
+Preparing Vegetables: Next, the vegetables should be prepped. The mixed bell peppers should be sliced into strips, adding both color and texture to the dish. Broccoli florets need to be bite-sized to ensure they cook quickly and evenly. Consistency in the size of your ingredients not only enhances presentation but also plays a big role in even cooking.
+Mincing Garlic: Lastly, it’s time to tackle the garlic. Use the flat edge of your knife to crush the cloves slightly—this makes peeling easier. A quick mince will do the trick, releasing those essential oils and fragrances that form the aromatic base of your dish.
+With these preparation steps complete, you’ll be ready to dive into the cooking process. The combination of minimal prep time and swift cooking makes this stir fry an excellent choice for any busy home cook. 
+## Cooking Instructions
+Now that you have everything prepped, it's time to ignite the cooking process that will bring your Easy 15-Minute Beef Stir Fry to life.
+First, heat the vegetable oil in a large skillet or wok over medium-high heat. It’s important to allow the pan to reach the right temperature, as this will ensure that you achieve that perfect sear on the beef. 
+Next, add the thinly sliced beef sirloin to the skillet. Cook for about 3-4 minutes while stirring frequently until the beef is browned. The sizzling of the beef hitting the hot oil adds an exciting auditory element to your cooking experience.
+Once the beef is browned, introduce the minced garlic to the pan. Cook for an additional minute, allowing the garlic to become fragrant without burning, as burnt garlic can impart a bitter taste. 
+Then, toss in the vibrant slices of mixed bell peppers and the broccoli florets. Stir well to incorporate all the ingredients, allowing their flavors to meld together beautifully. 
+Now, it’s time to pour the soy sauce and oyster sauce over the stir-fry. Mix everything together thoroughly, ensuring every ingredient is coated in the savory goodness from the sauces. 
+Finally, keep the stir fry cooking for another 2-3 minutes. You want the vegetables to become tender yet still retain their crispness—a hallmark of stir-fried dishes. 
+To finish, drizzle the sesame oil over the stir-fry and give it a final toss. This adds that last touch of nutty flavor that enhances the overall dish, making it irresistible.
+Your Easy 15-Minute Beef Stir Fry is now ready to be served over cooked rice or noodles, offering a perfect blend of taste, texture, and aromatics. This dish is sure to become a staple in your home rotation, perfect for those evenings when time is of the essence but a delicious meal is still desired.
+### Adding Aromatics: The Role of Garlic in Enhancing Flavors
+Aromatics are the backbone of many culinary dishes, and garlic plays a particularly pivotal role in enhancing flavors in the Easy 15-Minute Beef Stir Fry. When you mince garlic and add it to the hot skillet, a wonderful aroma fills the air, creating an enticing backdrop for the other ingredients. Garlic is not just about its strong scent; it also adds depth and richness to the dish. Cooking it briefly, just until fragrant, prevents bitterness and allows it to develop a sweet, mellow flavor. This essential step ensures that every bite of beef and vegetable is infused with the savory notes that garlic brings, elevating the overall taste of the stir fry.
+### Incorporating Vegetables: Techniques for Maintaining Texture and Color
+One of the hallmarks of a great stir fry is the texture and color of the vegetables. In the Easy 15-Minute Beef Stir Fry, vibrant mixed bell peppers and fresh broccoli florets contribute not only to the visual appeal but also to the nutritional balance of the dish. To maintain the crispiness and bright hues of the vegetables, it's crucial to follow certain techniques. 
+Firstly, high heat is your best friend. Cooking the vegetables quickly over medium-high heat allows them to cook through without becoming mushy. This method also helps them retain their vibrant colors, enhancing the overall presentation. Secondly, add the veggies at the appropriate time; once the beef has browned, introduce the garlic, then the bell peppers and broccoli. Stirring vigorously ensures even cooking and prevents sticking. Finally, aim for a tender-crisp texture where vegetables are cooked but still boast a satisfying snap. This technique showcases the fresh flavors, making your stir fry a visually stunning and well-balanced dish.
+Using Sauces: Tips for Achieving a Balanced Flavor Profile with Soy and Oyster Sauce
+Sauces are fundamental in a stir fry, providing the umami essence that ties the entire dish together. The Easy 15-Minute Beef Stir Fry utilizes soy sauce and oyster sauce, both of which play distinct roles in crafting the flavor profile. Soy sauce, with its salty and savory characteristics, acts as the primary seasoning, while oyster sauce adds a subtle sweetness and depth that enhances the overall richness of the dish.
+To achieve a balanced flavor, consider the ratios of these sauces. A recommended starting point is 2 tablespoons of soy sauce combined with 1 tablespoon of oyster sauce, as the recipe suggests. This proportion allows the salty notes to shine through while being complemented by the umami depth from the oyster sauce. It’s important to remember that different brands of sauces can vary in saltiness and flavor intensity; thus, taste-testing your sauce mixture before adding it to the stir fry can ensure balance and prevent overpowering the other flavors.
+### Final Touches: Utilizing Sesame Oil for Aroma and Flavor
+After thoroughly cooking your beef and vegetables, the final drizzle of sesame oil is more than just a finishing step; it’s an integral enhancement to the stir fry. Sesame oil is revered for its nutty flavor and aroma, which adds another layer of complexity. It’s typically used as a finishing oil rather than a cooking oil due to its lower smoke point, thus preserving its flavor when added at the end of the cooking process.
+When drizzling the sesame oil, it's best to use it sparingly—about 1 teaspoon is sufficient to impart its robust flavor without overwhelming the dish. Toss everything together one last time to ensure the oil coats the ingredients evenly. This final touch not only aromatizes the stir fry but also reinforces the Asian cuisine theme, making it a perfect close to your culinary creation.
+## Serving Suggestions
+### Recommended Accompaniments: Discussing the Best Types of Rice or Noodles to Use
+Serving the Easy 15-Minute Beef Stir Fry is about more than just placing the ingredients on a plate; choosing the right accompaniment can significantly enhance the dish. Traditionally, this stir fry pairs beautifully with both rice and noodles, depending on personal preference. 
+For rice, the options are plentiful. Fluffy white rice, jasmine rice, or even brown rice provide a neutral backdrop that allows the stir fry's bold flavors to take center stage. If you prefer noodles, consider using rice noodles, egg noodles, or udon for a hearty and satisfying meal. Each choice absorbs the savory sauces while balancing out the dish's richness.
+### Garnishes: Suggestions for Adding Freshness, Such as Green Onions or Sesame Seeds
+To elevate your beef stir fry visually and taste-wise, garnishing is essential. Fresh ingredients can brighten flavors and add a pop of color to your plate. A classic garnish for Asian dishes, sliced green onions not only provide a fresh crunch but also add a mild onion flavor that complements the richness of the beef. Sprinkling sesame seeds can offer a delightful finish, contributing a toasty flavor and textural contrast.
+Additional garnishes could include fresh cilantro or crispy fried shallots for additional depth and interest in flavor.
+Meal Prep Ideas: Ideas for Making This Dish in Bulk for Future Meals
+One of the many advantages of the Easy 15-Minute Beef Stir Fry is its adaptability for meal prep. Cooking in bulk allows you to enjoy this delightful dish multiple times throughout the week. To meal prep efficiently, simply double the ingredients and store individual portions in airtight containers after cooking.
+Make sure to keep rice or noodles separate to maintain their texture. This approach ensures that you have a quick, balance meal ready to reheat in minutes. Additionally, consider pre-chopping the vegetables and slicing the beef ahead of time; storing them in the fridge or freezer will cut down preparation time significantly.
+## Variations
+### Gluten-Free Options: Substitutions for Soy Sauce and Oyster Sauce
+For those with gluten sensitivities, enjoy this stir fry without compromising flavor by utilizing gluten-free sauces. There are several gluten-free soy sauce alternatives available, such as tamari or coconut aminos. These replace traditional soy sauce while maintaining a comparable level of saltiness. Similarly, gluten-free oyster sauce (or mushroom-based oyster sauce) can replicate the original flavor without the gluten.
+### Vegetarian Variations: Using Tofu or Tempeh Instead of Beef
+To create a vegetarian-friendly version of the beef stir fry, substitute the beef with plant-based proteins like tofu or tempeh. Firm tofu, when pressed to remove excess moisture and lightly pan-fried until golden, creates a satisfying texture that soaks up the marinades and sauces beautifully. Tempeh, made from fermented soybeans, adds a unique nutty flavor to the dish, providing a hearty backbone. 
+### Additional Vegetables: Suggestions for Extra Ingredients Like Snap Peas or Carrots
+The beauty of stir fry lies in its versatility. Feel free to customize this recipe by adding seasonal vegetables or personal favorites. Snap peas, broccoli stems, carrots, or even zucchini can bring freshness, color, and additional nutrients. Simply adjust cooking times slightly for denser vegetables to ensure everything reaches that perfect tender-crisp state while absorbing the delicious savory sauces.
+## Nutritional Information
+### Calories: Detail That It Contains Approximately 400 Calories per Serving
+The Easy 15-Minute Beef Stir Fry is not only quick to prepare but also offers a well-rounded meal option. Containing approximately 400 calories per serving, it satisfies without overwhelming calorie counts, making it an excellent choice for both nutritional balance and taste.
+### Protein Content: Discuss the Benefits of Lean Beef as a Protein Source
+This dish is an excellent source of protein thanks to the beef sirloin. Lean beef is rich in high-quality protein, essential for muscle growth and repair. It also provides critical nutrients such as iron, zinc, and vitamin B12, crucial for overall health and vitality. 
+### Vitamins and Minerals: Highlighting the Nutritional Benefits of Bell Peppers and Broccoli
+The addition of mixed bell peppers and broccoli not only enhances the stir fry's color and flavor but also boosts its nutrient profile. Bell peppers are high in vitamin C, an antioxidant that supports immune function and skin health. Broccoli, on the other hand, is rich in fiber and various vitamins, including vitamins K and A, providing an array of health benefits.
+## Cooking Tips and Tricks
+### Batch Cooking: Tips for Cooking in Larger Quantities While Maintaining Quality
+For those looking to cook in larger quantities, focus on batch cooking techniques that maintain the quality and flavor of the ingredients. When cooking larger portions, make sure to work in batches; overcrowding the skillet can lead to steaming rather than stir-frying, negatively impacting texture.
+### Storing Leftovers: Best Practices for Storing and Reheating
+If you find yourself with leftovers, ensure they are properly stored in airtight containers in the refrigerator. To reheat, using a skillet on medium heat will help regain the dish’s original texture, allowing you to enjoy the delightful flavors as if freshly prepared.
+### Avoiding Common Mistakes: Addressing Issues Like Overcooked Vegetables or Tough Beef
+A few common pitfalls can occur when making stir fries. To avoid overcooked vegetables, stick to high heat and minimal cook times. As for the beef, ensure it is sliced thinly against the grain for tenderness; marinating briefly can also help achieve the most succulent results.
+## Frequently Asked Questions
+Can I use frozen vegetables?
+Yes, using frozen vegetables can be a convenient option. However, it’s important to ensure they are fully thawed and pat them dry before adding them to the stir fry to prevent excess moisture.
+What if I don’t have oyster sauce?
+If oyster sauce is unavailable, you can substitute it with a combination of hoisin sauce or a mix of soy sauce with a hint of sugar, though it may slightly alter the flavor.
+How can I make this dish spicy?
+To introduce a spicy kick, consider adding red pepper flakes, sliced fresh chiles, or a spoonful of chili paste during cooking, allowing you to customize the heat level to your preference.
+## Conclusion
+The Easy 15-Minute Beef Stir Fry combines tender beef, crisp vegetables, and savory sauces into a quick and satisfying meal. With a total cooking time of just 15 minutes, it’s an exceptional option for busy weeknights or casual gatherings. The vibrant flavors and textures make this dish a favorite across generations, ensuring it can easily become a staple in any kitchen.
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve"># Easy Cheesy Loaded Potato Soup Recipe
+## Introduction
+Cheesy Loaded Potato Soup is the ultimate comfort food, embodying warmth and heartiness in every soothing bowl. This delightful dish marries the creaminess of heavy cream and cheddar cheese with the earthy goodness of russet potatoes, making it a favorite among families and gatherings. The inclusion of crumbled bacon and green onions adds a savory twist, enhancing the flavor profile that makes this soup truly irresistible.
+Perfect for chilly evenings, this soup serves as a nourishing main course that appeals to both adults and children alike. Whether you are hosting a casual dinner, preparing a weekend meal, or simply want to savor an evening indoors, this Cheesy Loaded Potato Soup will surely be a crowd-pleaser. Its simple preparation combined with the rich, comforting flavors makes it an ideal option for any occasion, be it family dinners or cozy gatherings with friends.
+## Recipe Overview
+- Prep Time: 10 minutes
+- Cook Time: 30 minutes
+- Total Time: 40 minutes
+- Course: Soup
+- Cuisine: American
+- Servings: 6
+- Calories: ~450 per serving
+### Description of Cheesy Loaded Potato Soup
+The Cheesy Loaded Potato Soup takes a classic recipe and elevates it with the addition of rich cheddar cheese and crispy bacon. It captivates the palate with a smooth texture and a satisfying layer of flavors, featuring the earthiness of potatoes balanced perfectly with creamy dairy elements. The soup is finished with fresh green onions, providing not just a pop of color but also a fresh bite that balances the richness.
+### Ideal Occasions for Serving
+This potato soup is incredibly versatile. It’s the kind of dish that can transition seamlessly from a casual weeknight dinner to a festive holiday gathering. When the weather turns cold, it offers a perfect homemade remedy that warms the soul. Serve it as a comforting centerpiece at a cozy family meal, or as a quick, hearty option alongside a fresh salad or crusty bread at a weekend brunch with friends. Furthermore, its appeal makes it perfect for potlucks and family events where comfort food is always a hit.
+### Nutritional Benefits of the Ingredients
+While Cheesy Loaded Potato Soup is indulgent and delicious, it also incorporates several ingredients that offer nutritional benefits. Potatoes are a great source of fiber and potassium, contributing to digestive health and heart health. The addition of onions and garlic provides antioxidants and anti-inflammatory properties, promoting overall well-being. Cheddar cheese delivers calcium and protein, making the soup not only comforting but also nourishing. The use of heavy cream adds a luscious texture while providing additional fats for energy, making this soup a satisfying dish.
+## Ingredients
+- 4 large russet potatoes, peeled and diced
+- 1 medium onion, chopped
+- 3 cloves garlic, minced
+- 4 cups chicken or vegetable broth
+- 1 cup heavy cream
+- 2 cups shredded cheddar cheese
+- 1/2 cup cooked and crumbled bacon
+- 1/4 cup green onions, chopped
+- Salt and pepper to taste
+### List of Required Ingredients
+The following ingredients serve as the perfect foundation for creating a flavorful Cheesy Loaded Potato Soup:
+- Russet potatoes are known for their starchy texture, making them ideal for soups.
+- Chopped onion and minced garlic provide aromatic flavors.
+- Chicken or vegetable broth forms the base of the soup, adding depth to the flavor.
+- Heavy cream contributes richness and creaminess to the dish.
+- Shredded cheddar cheese creates the signature cheesy layer that complements the potatoes beautifully.
+- Crumbled bacon infuses savory notes, while the green onions add a bright finish.
+- Salt and pepper are essential for seasoning and enhancing the overall flavor.
+### Insights on Ingredient Choices
+Choosing russet potatoes is key, as they break down nicely and thicken the soup. Onions and garlic not only contribute flavor but also encourage beneficial aromas that make the cooking process inviting. For rich flavor, opting for high-quality chicken or vegetable broth is beneficial, and using fresh, sharp cheddar cheese elevates the dish substantially. The crispiness of freshly cooked bacon introduces a delightful texture contrast, while the green onions introduce freshness to balance out the comforting richness.
+### Substitutions for Dietary Preferences
+For those with dietary restrictions or preferences, there are several potential substitutions. For a lighter version, consider using half-and-half in place of heavy cream, which will still offer creaminess with fewer calories. Vegan cheese can replace shredded cheddar for a dairy-free option, while plant-based cream alternatives work well to maintain the soup’s luscious consistency. If avoiding meat, substitute the bacon with smoked paprika to impart a similar flavor profile without the animal products.
+{{image_ing_1}}
+## Preparation Steps
+### Initial Preparations
+Begin by gathering all necessary ingredients and equipment. For this recipe, you will need a large pot for cooking and an immersion blender or traditional blender for achieving a smooth texture. Start by peeling and dicing the russet potatoes into small, even cubes. This step is crucial as it ensures even cooking throughout the soup. Chop the medium onion and mince the garlic to prepare for the flavor base.
+### Cooking the Soup
+In a large pot, combine the diced potatoes, chopped onion, minced garlic, and broth. It’s essential to use medium-high heat at this stage, bringing the mixture to a rolling boil, which helps the ingredients start to release their flavors. Once boiling, reduce the heat to low and allow the soup to simmer for approximately 15 to 20 minutes. This simmering phase is crucial—it allows the potatoes to soften and meld with the aromatic onion and garlic, resulting in a deeply flavorful broth.
+### Blending Techniques
+After the potatoes are tender, it’s time to transform the soup into a creamy delight. You can choose to use an immersion blender for convenience, carefully blending the soup until perfectly smooth while remaining in the pot. Alternatively, transferring the soup in batches to a traditional blender is possible—just ensure to allow it to cool slightly to prevent splattering. This blending step is vital for achieving the desired creamy texture that characterizes quality potato soup.
+## Cooking Techniques
+### Importance of Simmering
+Simmering is an essential cooking technique that allows the flavors to meld together beautifully. During this time, the potatoes' starches break down, naturally thickening the soup without the need for added thickeners. This gentle heat preserves the nutrients while enhancing the overall richness of flavor in the final soup. 
+### Using an Immersion Blender vs. Traditional Blender
+An immersion blender offers convenience and easier cleanup, allowing you to blend the soup directly in the cooking pot. Conversely, a traditional blender provides the same end result but requires transferring hot soup, a process that can be cumbersome if not done carefully. Both methods can yield a silky-smooth soup, but personal preference and comfort level in the kitchen will dictate the better choice for you.
+### Tips for Ensuring Creaminess in the Soup
+For an exceptionally creamy consistency, ensure that you incorporate the heavy cream slowly while stirring. This method promotes a uniform blend, resulting in an inviting texture. Opting for freshly shredded cheddar cheese rather than pre-packaged grated cheese can further enhance the creaminess, as the preservatives in pre-shredded cheese may alter the melting properties.
+The foundation for a flavorful and comforting Cheesy Loaded Potato Soup is set with proper preparation, cooking techniques, and ingredient selections. Through careful attention to detail, every bowl can be transformed into a creamy and indulgent experience fitting for any occasion.
+## Serving Suggestions
+Cheesy Loaded Potato Soup is not only satisfying by itself but can be enhanced further with thoughtful garnishes and accompaniments. Whether you’re serving this at a family gathering or a cozy night in, there are plenty of ways to elevate your soup experience.
+### Recommended Garnishes
+To add an extra layer of flavor and visual appeal to your Cheesy Loaded Potato Soup, consider including these garnishes:
+- **Extra Cheddar Cheese**: Sprinkle additional shredded cheddar on top of each bowl for that indulgent cheesy goodness.
+- **Chopped Green Onions**: Fresh green onions add a pop of color and balance the richness of the soup.
+- **Crispy Bacon Crumbles**: More crumbled bacon can amplify the smokiness and provide added texture.
+- **Sour Cream**: A dollop of sour cream on top can add creaminess and a delightful tang.
+- **Chili Flakes**: If you enjoy a bit of heat, sprinkle some chili flakes or paprika for a spicy kick.
+### Ideal Accompaniments for the Soup
+A hearty soup like this pairs wonderfully with a variety of side dishes, ensuring a well-rounded meal. Consider serving:
+- **Fresh Salad**: A crisp green salad featuring mixed greens, cherry tomatoes, and a light vinaigrette complements the richness of the soup.
+- **Garlic Bread**: Crunchy garlic bread or breadsticks provide a great vehicle for dipping and soaking up the creamy soup.
+- **Sandwiches**: Pair your soup with a classic grilled cheese or BLT sandwich for a comforting combo.
+### Creative Serving Ideas for Presentation
+Presentation can elevate the dining experience. Here are some creative ideas for serving your Cheesy Loaded Potato Soup:
+- **Serve in Bread Bowls**: Hollow out round loaves of bread and ladle the soup into these delightful bowls for a fun twist.
+- **Use Mason Jars**: For a rustic feel, serve the soup in mason jars, which are great for individual servings.
+- **Garnish with Fresh Herbs**: Enhance the visual appeal with fresh herbs like parsley or chives scattered around the soup.
+## Storage and Reheating
+Proper storage techniques can extend the life of your Cheesy Loaded Potato Soup while maintaining its delicious flavors. Here’s how to store it and reheat any leftovers.
+### Best Practices for Storage
+### To store your soup effectively:
+- **Transfer to Airtight Containers**: Allow the soup to cool before transferring it to airtight containers to keep it fresh.
+- **Refrigeration**: Store in the refrigerator for up to three days. Make sure it’s properly sealed to prevent any absorption of odors from other foods.
+- **Labeling**: If you’re storing it for a while, label your containers with the date to keep track of freshness.
+### How to Reheat Leftovers
+Reheating the soup correctly is essential to preserve its texture and flavor. Follow these steps:
+- **Stovetop Method**: Pour the desired amount of soup into a saucepan over medium heat. Stir occasionally until heated through. If the soup seems too thick, add a splash of broth or milk to achieve your preferred consistency.
+- **Microwave Method**: Place the soup in a microwave-safe bowl, covering it with a microwave-safe lid or plate. Heat on high for 1-2 minutes, stirring halfway through for even heating.
+### Freezing the Soup: What to Know
+If you want to store your Cheesy Loaded Potato Soup for a longer period, freezing is a great option. Here’s how:
+- **Allow to Cool Completely**: Before freezing, make sure the soup is completely cooled to prevent ice crystals from forming.
+- **Use Freezer-Safe Containers**: Transfer the soup into freezer-safe bags or containers, leaving some space at the top for expansion.
+- **Storage Duration**: It can be stored in the freezer for up to three months. Ensure that it’s well-sealed to avoid freezer burn.
+## Variations of Cheesy Loaded Potato Soup
+While the classic Cheesy Loaded Potato Soup is delicious, there are many variations to suit different dietary needs and preferences. Here are some ideas to make the soup your own.
+### Vegan Versions of the Soup
+### For a vegan twist, substitute non-dairy alternatives:
+- Replace heavy cream with coconut milk or cashew cream for a creamy consistency.
+- Use vegetable broth instead of chicken broth.
+- Opt for a plant-based cheese or nutritional yeast to retain that cheesy flavor without the dairy.
+### Gluten-Free Alternatives
+### If you require a gluten-free version, it’s simple to adapt:
+- Make sure to use gluten-free broth and check labels on any shredded cheese.
+- There’s no need for additional thickening agents, as the potatoes yield a creamy texture when blended.
+### Regional Twists on the Classic Recipe
+Exploring regional versions can also be exciting. Here are a couple of ideas:
+- **Chili Potato Soup**: Add some ground beef or turkey, kidney beans, and spices to create a chili-inspired take on the soup.
+- **Buffalo Loaded Potato Soup**: Incorporate buffalo sauce for a spicy kick and top with blue cheese crumbles and celery for added crunch.
+## Pairing Beverages
+Complementing your Cheesy Loaded Potato Soup with drinks can enhance the overall meal experience. Consider these beverage options:
+### Suggested Wines
+For those who enjoy wine, here are a few pairings that go well with the rich flavors:
+- **Chardonnay**: A full-bodied Chardonnay with buttery undertones complements the creaminess of the soup.
+- **Pinot Noir**: This light red wine offers enough acidity to cut through the richness of the cheese and cream.
+### Non-Alcoholic Options
+If you prefer non-alcoholic beverages, a variety of options complement the soup beautifully:
+- **Sparkling Water**: Refreshing sparkling water with a slice of lemon adds a sophisticated touch without overwhelming the flavors.
+- **Iced Tea**: Sweetened or unsweetened iced tea provides a delightful contrast to the rich soup.
+### Best Bread Choices to Accompany the Soup
+Bread is a classic side for soup, and some options work particularly well with Cheesy Loaded Potato Soup:
+- **Sourdough Bread**: The tanginess of sourdough pairs wonderfully with the creamy soup.
+- **Ciabatta Rolls**: Soft yet crusty, ciabatta rolls make for perfect dunking companions.
+## Frequently Asked Questions
+Many home cooks have common queries regarding Cheesy Loaded Potato Soup. Here are answers to some frequently asked questions.
+### Common Queries About the Recipe
+One recurring question is about the thickness of the soup. If you prefer a thinner consistency, simply add more broth or cream to achieve your desired texture. People also often wonder about making the soup ahead of time; yes, it can be made a day in advance and stored in the refrigerator.
+### Troubleshooting Tips
+In case your soup doesn’t come out as expected, here are a few troubleshooting tips:
+- **Too Thick**: If the soup is too thick for your liking, gradually stir in additional broth until you reach your preferred consistency.
+- **Lacking Flavor**: Adjust the seasoning. Adding salt, pepper, or herbs like thyme can enhance the overall flavor profile.
+### How to Customize the Soup Further
+Feel free to experiment with the base recipe. You can add vegetables such as corn, carrots, or even kale for added nutrition and flavor. If you want more protein, consider incorporating shredded chicken or white beans.
+## Conclusion
+In summary, Cheesy Loaded Potato Soup is a delicious and comforting dish that combines the heartiness of potatoes with the richness of cheddar cheese. The preparation time is minimal, making it an excellent option for a quick yet satisfying meal, and it delivers on flavor and texture with a creamy finish. This soup is perfect for warming up on a chilly day and can easily be adjusted to suit various tastes and dietary needs.
+</t>
+  </si>
+  <si>
+    <t>The Best Homemade Mac and Cheese Recipe</t>
+  </si>
+  <si>
+    <t>Easy Cheesy Loaded Potato Soup Recipe</t>
+  </si>
+  <si>
+    <t>Creamy Garlic Parmesan Chicken Pasta Recipe for a Delicious Dinner</t>
+  </si>
+  <si>
+    <t>Creamy Homemade Mac and Cheese Recipe for Ultimate Comfort Food</t>
+  </si>
+  <si>
+    <t>Quick 15-Minute Beef Stir Fry Recipe with Bell Peppers and Broccoli</t>
+  </si>
+  <si>
+    <t>Creamy Cheesy Loaded Potato Soup Recipe for Cozy Nights</t>
+  </si>
+  <si>
+    <t>Creamy Classic Mac and Cheese</t>
+  </si>
+  <si>
+    <t>Quick and Tasty Beef Stir Fry</t>
+  </si>
+  <si>
+    <t>Cheesy Loaded Potato Bliss</t>
+  </si>
+  <si>
+    <t>Indulge in a comforting bowl of creamy garlic Parmesan chicken pasta, perfect for a delicious dinner any night of the week. This easy Italian recipe features tender fettuccine tossed with succulent garlic chicken and a rich, cheesy sauce that will warm your soul. Treat yourself and your loved ones to this hearty dish that captures the essence of home-cooked goodness.</t>
+  </si>
+  <si>
+    <t>Indulge in the ultimate comfort food with this creamy homemade mac and cheese recipe that will warm your heart. Perfect for family gatherings or a cozy night in, this dish features a rich cheese sauce that elevates the classic macaroni and cheese experience. Embrace the flavors of American cuisine and bring a touch of nostalgia to your dining table with each delicious bite.</t>
+  </si>
+  <si>
+    <t>Discover the perfect quick meal with this 15-minute beef stir fry recipe featuring vibrant bell peppers and nutritious broccoli. This easy recipe brings the flavors of Asian cuisine to your dinner table, making it a healthy and satisfying option for busy weeknights. Enjoy a delicious dish that’s not only fast to prepare but also packed with fresh ingredients and taste.</t>
+  </si>
+  <si>
+    <t>Warm up your cozy nights with this creamy cheesy loaded potato soup recipe, perfect for comfort food lovers. This easy recipe brings together rich flavors in a delightful blend of potatoes and cheese, making it a staple in American cuisine. Enjoy a bowl of this heartwarming soup as you unwind and savor the season.</t>
+  </si>
+  <si>
+    <t>creamy pasta, garlic chicken, Parmesan cheese, fettuccine, Italian recipe, easy dinner</t>
+  </si>
+  <si>
+    <t>macaroni and cheese, homemade, baking, cheese sauce, comfort food, American cuisine</t>
+  </si>
+  <si>
+    <t>beef stir fry, easy recipe, quick meals, Asian cuisine, healthy dinner, 15-minute meal</t>
+  </si>
+  <si>
+    <t>cheesy soup, loaded potato, comfort food, creamy soup, easy recipe, American cuisine</t>
+  </si>
+  <si>
+    <t>Homemade Mac and Cheese</t>
+  </si>
+  <si>
+    <t>Beef Stir Fry</t>
+  </si>
+  <si>
+    <t>Indulge in creamy garlic Parmesan chicken pasta! A quick, delicious recipe perfect for dinner in just 30 minutes.</t>
+  </si>
+  <si>
+    <t>Discover the best homemade mac and cheese recipe that's creamy, cheesy, and sure to satisfy your cravings!</t>
+  </si>
+  <si>
+    <t>Enjoy a quick and delicious 15-minute beef stir fry, packed with veggies and flavors, perfect for a weeknight dinner!</t>
+  </si>
+  <si>
+    <t>Indulge in our Cheesy Loaded Potato Soup—rich, creamy, and filled with flavor. Perfect for a cozy meal any time!</t>
+  </si>
+  <si>
+    <t>Garlic Parmesan Chicken Fettuccine, Creamy Chicken Garlic Pasta, Alfredo Garlic Parmesan Pasta</t>
+  </si>
+  <si>
+    <t>Homemade Macaroni and Cheese, Crafted Mac and Cheese, DIY Mac and Cheese</t>
+  </si>
+  <si>
+    <t>Beef Sauté, Beef Stir-fried Dish, Beef Vegetable Stir-fry</t>
+  </si>
+  <si>
+    <t>Creamy Cheddar Potato Chowder, Cheddar-Infused Potato Soup, Rich Loaded Potato Bisque</t>
+  </si>
+  <si>
+    <t>dinner</t>
   </si>
 </sst>
 </file>
@@ -766,10 +1672,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:T3"/>
+  <dimension ref="A1:AJ5"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:36">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -830,141 +1736,489 @@
       <c r="T1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="U1" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="V1" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="W1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="X1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="Z1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AB1" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AC1" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AD1" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AE1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AF1" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AG1" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AH1" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AI1" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AJ1" s="1" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="2" spans="1:20">
+    <row r="2" spans="1:36">
       <c r="A2" t="s">
-        <v>20</v>
+        <v>36</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>44</v>
       </c>
       <c r="D2" t="s">
-        <v>26</v>
+        <v>48</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>52</v>
       </c>
       <c r="F2" t="s">
-        <v>30</v>
-      </c>
-      <c r="G2" s="2" t="s">
-        <v>32</v>
+        <v>56</v>
+      </c>
+      <c r="G2" t="s">
+        <v>60</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>34</v>
+        <v>64</v>
       </c>
       <c r="I2" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>76</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>80</v>
+      </c>
+      <c r="M2" t="s">
+        <v>84</v>
+      </c>
+      <c r="O2" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="P2" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="Q2" s="2" t="s">
+        <v>93</v>
+      </c>
+      <c r="R2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="S2" s="2" t="s">
+        <v>101</v>
+      </c>
+      <c r="T2" t="s">
+        <v>84</v>
+      </c>
+      <c r="V2" t="s">
+        <v>105</v>
+      </c>
+      <c r="W2" t="s">
+        <v>106</v>
+      </c>
+      <c r="X2" t="s">
         <v>36</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="Y2">
+        <v>1</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>112</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AB2" t="s">
+        <v>119</v>
+      </c>
+      <c r="AC2" t="s">
+        <v>123</v>
+      </c>
+      <c r="AD2" t="s">
+        <v>36</v>
+      </c>
+      <c r="AE2" t="s">
+        <v>129</v>
+      </c>
+      <c r="AF2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AG2" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:36">
+      <c r="A3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B3" t="s">
+        <v>41</v>
+      </c>
+      <c r="C3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E3" t="s">
+        <v>53</v>
+      </c>
+      <c r="F3" t="s">
+        <v>57</v>
+      </c>
+      <c r="G3" t="s">
+        <v>61</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>77</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>81</v>
+      </c>
+      <c r="M3" t="s">
+        <v>84</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="T3" t="s">
+        <v>84</v>
+      </c>
+      <c r="V3" t="s">
+        <v>105</v>
+      </c>
+      <c r="W3" t="s">
+        <v>107</v>
+      </c>
+      <c r="X3" t="s">
+        <v>110</v>
+      </c>
+      <c r="Y3">
+        <v>2</v>
+      </c>
+      <c r="Z3" t="s">
+        <v>113</v>
+      </c>
+      <c r="AA3" t="s">
+        <v>116</v>
+      </c>
+      <c r="AB3" t="s">
+        <v>120</v>
+      </c>
+      <c r="AC3" t="s">
+        <v>124</v>
+      </c>
+      <c r="AD3" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE3" t="s">
+        <v>130</v>
+      </c>
+      <c r="AF3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AG3" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:36">
+      <c r="A4" t="s">
         <v>38</v>
       </c>
-      <c r="K2" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="L2" t="s">
+      <c r="B4" t="s">
         <v>42</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="C4" t="s">
+        <v>46</v>
+      </c>
+      <c r="D4" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" t="s">
+        <v>54</v>
+      </c>
+      <c r="F4" t="s">
+        <v>58</v>
+      </c>
+      <c r="G4" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="I4" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="L4" s="2" t="s">
+        <v>82</v>
+      </c>
+      <c r="M4" t="s">
+        <v>84</v>
+      </c>
+      <c r="O4" s="2" t="s">
+        <v>87</v>
+      </c>
+      <c r="P4" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="Q4" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="R4" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="S4" s="2" t="s">
+        <v>103</v>
+      </c>
+      <c r="T4" t="s">
+        <v>84</v>
+      </c>
+      <c r="V4" t="s">
+        <v>105</v>
+      </c>
+      <c r="W4" t="s">
+        <v>108</v>
+      </c>
+      <c r="X4" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y4">
+        <v>3</v>
+      </c>
+      <c r="Z4" t="s">
+        <v>114</v>
+      </c>
+      <c r="AA4" t="s">
+        <v>117</v>
+      </c>
+      <c r="AB4" t="s">
+        <v>121</v>
+      </c>
+      <c r="AC4" t="s">
+        <v>125</v>
+      </c>
+      <c r="AD4" t="s">
+        <v>128</v>
+      </c>
+      <c r="AE4" t="s">
+        <v>131</v>
+      </c>
+      <c r="AF4" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG4" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="5" spans="1:36">
+      <c r="A5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B5" t="s">
         <v>43</v>
       </c>
-      <c r="O2" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="P2" s="2" t="s">
+      <c r="C5" t="s">
         <v>47</v>
       </c>
-      <c r="Q2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="R2" s="2" t="s">
+      <c r="D5" t="s">
         <v>51</v>
       </c>
-      <c r="S2" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="3" spans="1:20">
-      <c r="A3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
-      <c r="F3" t="s">
-        <v>31</v>
-      </c>
-      <c r="G3" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="E5" t="s">
+        <v>55</v>
+      </c>
+      <c r="F5" t="s">
+        <v>59</v>
+      </c>
+      <c r="G5" t="s">
+        <v>63</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="I5" s="2" t="s">
+        <v>71</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>79</v>
+      </c>
+      <c r="L5" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="M5" t="s">
+        <v>84</v>
+      </c>
+      <c r="O5" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="P5" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="Q5" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="T5" t="s">
+        <v>84</v>
+      </c>
+      <c r="V5" t="s">
+        <v>105</v>
+      </c>
+      <c r="W5" t="s">
+        <v>109</v>
+      </c>
+      <c r="X5" t="s">
+        <v>111</v>
+      </c>
+      <c r="Y5">
+        <v>4</v>
+      </c>
+      <c r="Z5" t="s">
+        <v>115</v>
+      </c>
+      <c r="AA5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AB5" t="s">
+        <v>122</v>
+      </c>
+      <c r="AC5" t="s">
+        <v>126</v>
+      </c>
+      <c r="AD5" t="s">
         <v>39</v>
       </c>
-      <c r="K3" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L3" t="s">
-        <v>42</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="S3" t="s">
-        <v>42</v>
+      <c r="AE5" t="s">
+        <v>132</v>
+      </c>
+      <c r="AF5" t="s">
+        <v>136</v>
+      </c>
+      <c r="AG5" t="s">
+        <v>137</v>
+      </c>
+      <c r="AH5">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="G2" r:id="rId1"/>
-    <hyperlink ref="H2" r:id="rId2"/>
-    <hyperlink ref="I2" r:id="rId3"/>
-    <hyperlink ref="J2" r:id="rId4"/>
-    <hyperlink ref="K2" r:id="rId5"/>
-    <hyperlink ref="N2" r:id="rId6"/>
-    <hyperlink ref="O2" r:id="rId7"/>
-    <hyperlink ref="P2" r:id="rId8"/>
-    <hyperlink ref="Q2" r:id="rId9"/>
-    <hyperlink ref="R2" r:id="rId10"/>
-    <hyperlink ref="G3" r:id="rId11"/>
-    <hyperlink ref="H3" r:id="rId12"/>
-    <hyperlink ref="I3" r:id="rId13"/>
-    <hyperlink ref="J3" r:id="rId14"/>
-    <hyperlink ref="K3" r:id="rId15"/>
-    <hyperlink ref="N3" r:id="rId16"/>
-    <hyperlink ref="O3" r:id="rId17"/>
-    <hyperlink ref="P3" r:id="rId18"/>
-    <hyperlink ref="Q3" r:id="rId19"/>
-    <hyperlink ref="R3" r:id="rId20"/>
+    <hyperlink ref="H2" r:id="rId1"/>
+    <hyperlink ref="I2" r:id="rId2"/>
+    <hyperlink ref="J2" r:id="rId3"/>
+    <hyperlink ref="K2" r:id="rId4"/>
+    <hyperlink ref="L2" r:id="rId5"/>
+    <hyperlink ref="O2" r:id="rId6"/>
+    <hyperlink ref="P2" r:id="rId7"/>
+    <hyperlink ref="Q2" r:id="rId8"/>
+    <hyperlink ref="R2" r:id="rId9"/>
+    <hyperlink ref="S2" r:id="rId10"/>
+    <hyperlink ref="H3" r:id="rId11"/>
+    <hyperlink ref="I3" r:id="rId12"/>
+    <hyperlink ref="J3" r:id="rId13"/>
+    <hyperlink ref="K3" r:id="rId14"/>
+    <hyperlink ref="L3" r:id="rId15"/>
+    <hyperlink ref="O3" r:id="rId16"/>
+    <hyperlink ref="P3" r:id="rId17"/>
+    <hyperlink ref="Q3" r:id="rId18"/>
+    <hyperlink ref="R3" r:id="rId19"/>
+    <hyperlink ref="S3" r:id="rId20"/>
+    <hyperlink ref="H4" r:id="rId21"/>
+    <hyperlink ref="I4" r:id="rId22"/>
+    <hyperlink ref="J4" r:id="rId23"/>
+    <hyperlink ref="K4" r:id="rId24"/>
+    <hyperlink ref="L4" r:id="rId25"/>
+    <hyperlink ref="O4" r:id="rId26"/>
+    <hyperlink ref="P4" r:id="rId27"/>
+    <hyperlink ref="Q4" r:id="rId28"/>
+    <hyperlink ref="R4" r:id="rId29"/>
+    <hyperlink ref="S4" r:id="rId30"/>
+    <hyperlink ref="H5" r:id="rId31"/>
+    <hyperlink ref="I5" r:id="rId32"/>
+    <hyperlink ref="J5" r:id="rId33"/>
+    <hyperlink ref="K5" r:id="rId34"/>
+    <hyperlink ref="L5" r:id="rId35"/>
+    <hyperlink ref="O5" r:id="rId36"/>
+    <hyperlink ref="P5" r:id="rId37"/>
+    <hyperlink ref="Q5" r:id="rId38"/>
+    <hyperlink ref="R5" r:id="rId39"/>
+    <hyperlink ref="S5" r:id="rId40"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
